--- a/research/traditional_assets/database/data/mongolia/mongolia_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/mongolia/mongolia_metals_mining.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1607013260960539</v>
+        <v>0.1603333227808138</v>
       </c>
       <c r="C2">
-        <v>3047.23774850935</v>
+        <v>3026.471998639626</v>
       </c>
       <c r="D2">
-        <v>2972.93774850935</v>
+        <v>2982.489998639626</v>
       </c>
       <c r="E2">
-        <v>-232.9</v>
+        <v>-202.582</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30.318</v>
       </c>
       <c r="G2">
         <v>74.3</v>
@@ -1445,28 +1445,28 @@
         <v>309.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.5249954</v>
       </c>
       <c r="N2">
-        <v>309.1</v>
+        <v>307.5750046</v>
       </c>
       <c r="O2">
-        <v>77.27500000000001</v>
+        <v>76.89375115</v>
       </c>
       <c r="P2">
-        <v>231.825</v>
+        <v>230.68125345</v>
       </c>
       <c r="Q2">
-        <v>316.125</v>
+        <v>314.9812534499999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1607013260960539</v>
+        <v>0.1615717906876907</v>
       </c>
       <c r="T2">
-        <v>0.9842199092652958</v>
+        <v>0.9916761206991238</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>202.6891359803446</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1603333227808138</v>
+        <v>0.1599653194655737</v>
       </c>
       <c r="C3">
-        <v>3026.471998639626</v>
+        <v>3005.767830688691</v>
       </c>
       <c r="D3">
-        <v>2982.489998639626</v>
+        <v>2992.103830688691</v>
       </c>
       <c r="E3">
-        <v>-202.582</v>
+        <v>-172.264</v>
       </c>
       <c r="F3">
-        <v>30.318</v>
+        <v>60.636</v>
       </c>
       <c r="G3">
         <v>74.3</v>
@@ -1527,28 +1527,28 @@
         <v>309.1</v>
       </c>
       <c r="M3">
-        <v>1.5249954</v>
+        <v>3.0499908</v>
       </c>
       <c r="N3">
-        <v>307.5750046</v>
+        <v>306.0500092</v>
       </c>
       <c r="O3">
-        <v>76.89375115</v>
+        <v>76.51250230000001</v>
       </c>
       <c r="P3">
-        <v>230.68125345</v>
+        <v>229.5375069</v>
       </c>
       <c r="Q3">
-        <v>314.9812534499999</v>
+        <v>313.8375069</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1615717906876907</v>
+        <v>0.1624600198628303</v>
       </c>
       <c r="T3">
-        <v>0.9916761206991238</v>
+        <v>0.9992844997132341</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>202.6891359803446</v>
+        <v>101.3445679901723</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1599653194655737</v>
+        <v>0.1595973161503335</v>
       </c>
       <c r="C4">
-        <v>3005.767830688691</v>
+        <v>2985.125842096391</v>
       </c>
       <c r="D4">
-        <v>2992.103830688691</v>
+        <v>3001.779842096391</v>
       </c>
       <c r="E4">
-        <v>-172.264</v>
+        <v>-141.946</v>
       </c>
       <c r="F4">
-        <v>60.636</v>
+        <v>90.95400000000001</v>
       </c>
       <c r="G4">
         <v>74.3</v>
@@ -1609,28 +1609,28 @@
         <v>309.1</v>
       </c>
       <c r="M4">
-        <v>3.0499908</v>
+        <v>4.574986200000001</v>
       </c>
       <c r="N4">
-        <v>306.0500092</v>
+        <v>304.5250138</v>
       </c>
       <c r="O4">
-        <v>76.51250230000001</v>
+        <v>76.13125345</v>
       </c>
       <c r="P4">
-        <v>229.5375069</v>
+        <v>228.39376035</v>
       </c>
       <c r="Q4">
-        <v>313.8375069</v>
+        <v>312.6937603499999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1624600198628303</v>
+        <v>0.163366563041581</v>
       </c>
       <c r="T4">
-        <v>0.9992844997132341</v>
+        <v>1.007049752521449</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>101.3445679901723</v>
+        <v>67.56304532678152</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1595973161503335</v>
+        <v>0.1592293128350934</v>
       </c>
       <c r="C5">
-        <v>2985.125842096391</v>
+        <v>2964.54663805576</v>
       </c>
       <c r="D5">
-        <v>3001.779842096391</v>
+        <v>3011.51863805576</v>
       </c>
       <c r="E5">
-        <v>-141.946</v>
+        <v>-111.628</v>
       </c>
       <c r="F5">
-        <v>90.95400000000001</v>
+        <v>121.272</v>
       </c>
       <c r="G5">
         <v>74.3</v>
@@ -1691,28 +1691,28 @@
         <v>309.1</v>
       </c>
       <c r="M5">
-        <v>4.574986200000001</v>
+        <v>6.0999816</v>
       </c>
       <c r="N5">
-        <v>304.5250138</v>
+        <v>303.0000184</v>
       </c>
       <c r="O5">
-        <v>76.13125345</v>
+        <v>75.75000460000001</v>
       </c>
       <c r="P5">
-        <v>228.39376035</v>
+        <v>227.2500138</v>
       </c>
       <c r="Q5">
-        <v>312.6937603499999</v>
+        <v>311.5500138</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.163366563041581</v>
+        <v>0.1642919925365556</v>
       </c>
       <c r="T5">
-        <v>1.007049752521449</v>
+        <v>1.014976781429836</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>67.56304532678152</v>
+        <v>50.67228399508616</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1592293128350934</v>
+        <v>0.1588613095198532</v>
       </c>
       <c r="C6">
-        <v>2964.54663805576</v>
+        <v>2944.030831639211</v>
       </c>
       <c r="D6">
-        <v>3011.51863805576</v>
+        <v>3021.320831639211</v>
       </c>
       <c r="E6">
-        <v>-111.628</v>
+        <v>-81.30999999999997</v>
       </c>
       <c r="F6">
-        <v>121.272</v>
+        <v>151.59</v>
       </c>
       <c r="G6">
         <v>74.3</v>
@@ -1773,28 +1773,28 @@
         <v>309.1</v>
       </c>
       <c r="M6">
-        <v>6.0999816</v>
+        <v>7.624976999999999</v>
       </c>
       <c r="N6">
-        <v>303.0000184</v>
+        <v>301.475023</v>
       </c>
       <c r="O6">
-        <v>75.75000460000001</v>
+        <v>75.36875575000001</v>
       </c>
       <c r="P6">
-        <v>227.2500138</v>
+        <v>226.10626725</v>
       </c>
       <c r="Q6">
-        <v>311.5500138</v>
+        <v>310.40626725</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1642919925365556</v>
+        <v>0.1652369047577403</v>
       </c>
       <c r="T6">
-        <v>1.014976781429836</v>
+        <v>1.023070695157347</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.67228399508616</v>
+        <v>40.53782719606892</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1588613095198532</v>
+        <v>0.1584933062046131</v>
       </c>
       <c r="C7">
-        <v>2944.030831639211</v>
+        <v>2923.579043927175</v>
       </c>
       <c r="D7">
-        <v>3021.320831639211</v>
+        <v>3031.187043927175</v>
       </c>
       <c r="E7">
-        <v>-81.30999999999997</v>
+        <v>-50.99199999999996</v>
       </c>
       <c r="F7">
-        <v>151.59</v>
+        <v>181.908</v>
       </c>
       <c r="G7">
         <v>74.3</v>
@@ -1855,28 +1855,28 @@
         <v>309.1</v>
       </c>
       <c r="M7">
-        <v>7.624976999999999</v>
+        <v>9.149972400000001</v>
       </c>
       <c r="N7">
-        <v>301.475023</v>
+        <v>299.9500276</v>
       </c>
       <c r="O7">
-        <v>75.36875575000001</v>
+        <v>74.9875069</v>
       </c>
       <c r="P7">
-        <v>226.10626725</v>
+        <v>224.9625207</v>
       </c>
       <c r="Q7">
-        <v>310.40626725</v>
+        <v>309.2625207</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1652369047577403</v>
+        <v>0.1662019214942693</v>
       </c>
       <c r="T7">
-        <v>1.023070695157347</v>
+        <v>1.03133681981523</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.53782719606892</v>
+        <v>33.78152266339076</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1584933062046131</v>
+        <v>0.158125302889373</v>
       </c>
       <c r="C8">
-        <v>2923.579043927175</v>
+        <v>2903.191904139293</v>
       </c>
       <c r="D8">
-        <v>3031.187043927175</v>
+        <v>3041.117904139293</v>
       </c>
       <c r="E8">
-        <v>-50.99199999999996</v>
+        <v>-20.67399999999998</v>
       </c>
       <c r="F8">
-        <v>181.908</v>
+        <v>212.226</v>
       </c>
       <c r="G8">
         <v>74.3</v>
@@ -1937,28 +1937,28 @@
         <v>309.1</v>
       </c>
       <c r="M8">
-        <v>9.149972400000001</v>
+        <v>10.6749678</v>
       </c>
       <c r="N8">
-        <v>299.9500276</v>
+        <v>298.4250322</v>
       </c>
       <c r="O8">
-        <v>74.9875069</v>
+        <v>74.60625805000001</v>
       </c>
       <c r="P8">
-        <v>224.9625207</v>
+        <v>223.81877415</v>
       </c>
       <c r="Q8">
-        <v>309.2625207</v>
+        <v>308.11877415</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1662019214942693</v>
+        <v>0.1671876912788957</v>
       </c>
       <c r="T8">
-        <v>1.03133681981523</v>
+        <v>1.039780710594788</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.78152266339076</v>
+        <v>28.95559085433495</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.158125302889373</v>
+        <v>0.1577572995741329</v>
       </c>
       <c r="C9">
-        <v>2903.191904139294</v>
+        <v>2882.870049768175</v>
       </c>
       <c r="D9">
-        <v>3041.117904139294</v>
+        <v>3051.114049768174</v>
       </c>
       <c r="E9">
-        <v>-20.67399999999995</v>
+        <v>9.644000000000034</v>
       </c>
       <c r="F9">
-        <v>212.226</v>
+        <v>242.544</v>
       </c>
       <c r="G9">
         <v>74.3</v>
@@ -2019,28 +2019,28 @@
         <v>309.1</v>
       </c>
       <c r="M9">
-        <v>10.6749678</v>
+        <v>12.1999632</v>
       </c>
       <c r="N9">
-        <v>298.4250322</v>
+        <v>296.9000368</v>
       </c>
       <c r="O9">
-        <v>74.60625805000001</v>
+        <v>74.2250092</v>
       </c>
       <c r="P9">
-        <v>223.81877415</v>
+        <v>222.6750276</v>
       </c>
       <c r="Q9">
-        <v>308.11877415</v>
+        <v>306.9750276</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1671876912788957</v>
+        <v>0.1681948908414488</v>
       </c>
       <c r="T9">
-        <v>1.039780710594788</v>
+        <v>1.04840816421738</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.95559085433494</v>
+        <v>25.33614199754308</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1577572995741329</v>
+        <v>0.1573892962588927</v>
       </c>
       <c r="C10">
-        <v>2882.870049768175</v>
+        <v>2862.614126715819</v>
       </c>
       <c r="D10">
-        <v>3051.114049768174</v>
+        <v>3061.176126715819</v>
       </c>
       <c r="E10">
-        <v>9.644000000000034</v>
+        <v>39.96200000000005</v>
       </c>
       <c r="F10">
-        <v>242.544</v>
+        <v>272.862</v>
       </c>
       <c r="G10">
         <v>74.3</v>
@@ -2101,28 +2101,28 @@
         <v>309.1</v>
       </c>
       <c r="M10">
-        <v>12.1999632</v>
+        <v>13.7249586</v>
       </c>
       <c r="N10">
-        <v>296.9000368</v>
+        <v>295.3750414</v>
       </c>
       <c r="O10">
-        <v>74.2250092</v>
+        <v>73.84376035000001</v>
       </c>
       <c r="P10">
-        <v>222.6750276</v>
+        <v>221.53128105</v>
       </c>
       <c r="Q10">
-        <v>306.9750276</v>
+        <v>305.83128105</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1681948908414488</v>
+        <v>0.1692242266581239</v>
       </c>
       <c r="T10">
-        <v>1.04840816421738</v>
+        <v>1.057225232205304</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.33614199754308</v>
+        <v>22.52101510892718</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1573892962588927</v>
+        <v>0.1570212929436526</v>
       </c>
       <c r="C11">
-        <v>2862.614126715819</v>
+        <v>2842.424789432734</v>
       </c>
       <c r="D11">
-        <v>3061.176126715819</v>
+        <v>3071.304789432733</v>
       </c>
       <c r="E11">
-        <v>39.96200000000005</v>
+        <v>70.28000000000003</v>
       </c>
       <c r="F11">
-        <v>272.862</v>
+        <v>303.18</v>
       </c>
       <c r="G11">
         <v>74.3</v>
@@ -2183,28 +2183,28 @@
         <v>309.1</v>
       </c>
       <c r="M11">
-        <v>13.7249586</v>
+        <v>15.249954</v>
       </c>
       <c r="N11">
-        <v>295.3750414</v>
+        <v>293.850046</v>
       </c>
       <c r="O11">
-        <v>73.84376035000001</v>
+        <v>73.46251150000001</v>
       </c>
       <c r="P11">
-        <v>221.53128105</v>
+        <v>220.3875345</v>
       </c>
       <c r="Q11">
-        <v>305.83128105</v>
+        <v>304.6875345</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1692242266581239</v>
+        <v>0.1702764366040584</v>
       </c>
       <c r="T11">
-        <v>1.057225232205304</v>
+        <v>1.066238235037404</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.52101510892718</v>
+        <v>20.26891359803446</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1570212929436526</v>
+        <v>0.1566532896284125</v>
       </c>
       <c r="C12">
-        <v>2842.424789432734</v>
+        <v>2822.302701059829</v>
       </c>
       <c r="D12">
-        <v>3071.304789432733</v>
+        <v>3081.500701059829</v>
       </c>
       <c r="E12">
-        <v>70.28000000000003</v>
+        <v>100.5980000000001</v>
       </c>
       <c r="F12">
-        <v>303.18</v>
+        <v>333.498</v>
       </c>
       <c r="G12">
         <v>74.3</v>
@@ -2265,28 +2265,28 @@
         <v>309.1</v>
       </c>
       <c r="M12">
-        <v>15.249954</v>
+        <v>16.7749494</v>
       </c>
       <c r="N12">
-        <v>293.850046</v>
+        <v>292.3250506</v>
       </c>
       <c r="O12">
-        <v>73.46251150000001</v>
+        <v>73.08126265</v>
       </c>
       <c r="P12">
-        <v>220.3875345</v>
+        <v>219.24378795</v>
       </c>
       <c r="Q12">
-        <v>304.6875345</v>
+        <v>303.54378795</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1702764366040584</v>
+        <v>0.1713522917173174</v>
       </c>
       <c r="T12">
-        <v>1.066238235037404</v>
+        <v>1.075453777258989</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.26891359803446</v>
+        <v>18.42628508912223</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1566532896284125</v>
+        <v>0.1562852863131723</v>
       </c>
       <c r="C13">
-        <v>2822.302701059829</v>
+        <v>2802.248533573151</v>
       </c>
       <c r="D13">
-        <v>3081.500701059829</v>
+        <v>3091.76453357315</v>
       </c>
       <c r="E13">
-        <v>100.5980000000001</v>
+        <v>130.9160000000001</v>
       </c>
       <c r="F13">
-        <v>333.498</v>
+        <v>363.816</v>
       </c>
       <c r="G13">
         <v>74.3</v>
@@ -2347,28 +2347,28 @@
         <v>309.1</v>
       </c>
       <c r="M13">
-        <v>16.7749494</v>
+        <v>18.2999448</v>
       </c>
       <c r="N13">
-        <v>292.3250506</v>
+        <v>290.8000552</v>
       </c>
       <c r="O13">
-        <v>73.08126265</v>
+        <v>72.70001380000001</v>
       </c>
       <c r="P13">
-        <v>219.24378795</v>
+        <v>218.1000414</v>
       </c>
       <c r="Q13">
-        <v>303.54378795</v>
+        <v>302.4000414</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1713522917173174</v>
+        <v>0.1724525980831504</v>
       </c>
       <c r="T13">
-        <v>1.075453777258989</v>
+        <v>1.084878763621974</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.42628508912223</v>
+        <v>16.89076133169538</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1562852863131723</v>
+        <v>0.1559172829979322</v>
       </c>
       <c r="C14">
-        <v>2802.248533573151</v>
+        <v>2782.262967931508</v>
       </c>
       <c r="D14">
-        <v>3091.76453357315</v>
+        <v>3102.096967931508</v>
       </c>
       <c r="E14">
-        <v>130.9160000000001</v>
+        <v>161.234</v>
       </c>
       <c r="F14">
-        <v>363.816</v>
+        <v>394.134</v>
       </c>
       <c r="G14">
         <v>74.3</v>
@@ -2429,28 +2429,28 @@
         <v>309.1</v>
       </c>
       <c r="M14">
-        <v>18.2999448</v>
+        <v>19.8249402</v>
       </c>
       <c r="N14">
-        <v>290.8000552</v>
+        <v>289.2750598</v>
       </c>
       <c r="O14">
-        <v>72.70001380000001</v>
+        <v>72.31876495</v>
       </c>
       <c r="P14">
-        <v>218.1000414</v>
+        <v>216.95629485</v>
       </c>
       <c r="Q14">
-        <v>302.4000414</v>
+        <v>301.25629485</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1724525980831504</v>
+        <v>0.1735781988481979</v>
       </c>
       <c r="T14">
-        <v>1.084878763621974</v>
+        <v>1.094520416338131</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.89076133169538</v>
+        <v>15.59147199848805</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1559172829979322</v>
+        <v>0.155549279682692</v>
       </c>
       <c r="C15">
-        <v>2782.262967931508</v>
+        <v>2762.346694227077</v>
       </c>
       <c r="D15">
-        <v>3102.096967931508</v>
+        <v>3112.498694227078</v>
       </c>
       <c r="E15">
-        <v>161.234</v>
+        <v>191.5520000000001</v>
       </c>
       <c r="F15">
-        <v>394.134</v>
+        <v>424.4520000000001</v>
       </c>
       <c r="G15">
         <v>74.3</v>
@@ -2511,28 +2511,28 @@
         <v>309.1</v>
       </c>
       <c r="M15">
-        <v>19.8249402</v>
+        <v>21.3499356</v>
       </c>
       <c r="N15">
-        <v>289.2750598</v>
+        <v>287.7500644</v>
       </c>
       <c r="O15">
-        <v>72.31876495</v>
+        <v>71.93751610000001</v>
       </c>
       <c r="P15">
-        <v>216.95629485</v>
+        <v>215.8125483</v>
       </c>
       <c r="Q15">
-        <v>301.25629485</v>
+        <v>300.1125483</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1735781988481979</v>
+        <v>0.1747299763752233</v>
       </c>
       <c r="T15">
-        <v>1.094520416338131</v>
+        <v>1.104386293536059</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.59147199848805</v>
+        <v>14.47779542716747</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.155549279682692</v>
+        <v>0.1551812763674519</v>
       </c>
       <c r="C16">
-        <v>2762.346694227077</v>
+        <v>2742.500411839041</v>
       </c>
       <c r="D16">
-        <v>3112.498694227078</v>
+        <v>3122.970411839041</v>
       </c>
       <c r="E16">
-        <v>191.5520000000001</v>
+        <v>221.8700000000001</v>
       </c>
       <c r="F16">
-        <v>424.4520000000001</v>
+        <v>454.7700000000001</v>
       </c>
       <c r="G16">
         <v>74.3</v>
@@ -2593,28 +2593,28 @@
         <v>309.1</v>
       </c>
       <c r="M16">
-        <v>21.3499356</v>
+        <v>22.874931</v>
       </c>
       <c r="N16">
-        <v>287.7500644</v>
+        <v>286.225069</v>
       </c>
       <c r="O16">
-        <v>71.93751610000001</v>
+        <v>71.55626725</v>
       </c>
       <c r="P16">
-        <v>215.8125483</v>
+        <v>214.66880175</v>
       </c>
       <c r="Q16">
-        <v>300.1125483</v>
+        <v>298.96880175</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1747299763752233</v>
+        <v>0.1759088545499434</v>
       </c>
       <c r="T16">
-        <v>1.104386293536059</v>
+        <v>1.114484309020997</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.47779542716747</v>
+        <v>13.5126090653563</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1551812763674519</v>
+        <v>0.1549932730522118</v>
       </c>
       <c r="C17">
-        <v>2742.500411839041</v>
+        <v>2717.559380350112</v>
       </c>
       <c r="D17">
-        <v>3122.970411839041</v>
+        <v>3128.347380350112</v>
       </c>
       <c r="E17">
-        <v>221.8700000000001</v>
+        <v>252.188</v>
       </c>
       <c r="F17">
-        <v>454.77</v>
+        <v>485.088</v>
       </c>
       <c r="G17">
         <v>74.3</v>
@@ -2675,45 +2675,45 @@
         <v>309.1</v>
       </c>
       <c r="M17">
-        <v>22.874931</v>
+        <v>25.1275584</v>
       </c>
       <c r="N17">
-        <v>286.225069</v>
+        <v>283.9724416</v>
       </c>
       <c r="O17">
-        <v>71.55626725</v>
+        <v>70.99311040000001</v>
       </c>
       <c r="P17">
-        <v>214.66880175</v>
+        <v>212.9793312</v>
       </c>
       <c r="Q17">
-        <v>298.96880175</v>
+        <v>297.2793312</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1759088545499434</v>
+        <v>0.1771158012526331</v>
       </c>
       <c r="T17">
-        <v>1.114484309020997</v>
+        <v>1.124822753446052</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.51260906535631</v>
+        <v>12.30123496598858</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1549932730522118</v>
+        <v>0.1546365197369717</v>
       </c>
       <c r="C18">
-        <v>2717.559380350112</v>
+        <v>2697.495735247346</v>
       </c>
       <c r="D18">
-        <v>3128.347380350112</v>
+        <v>3138.601735247345</v>
       </c>
       <c r="E18">
-        <v>252.188</v>
+        <v>282.5060000000001</v>
       </c>
       <c r="F18">
-        <v>485.088</v>
+        <v>515.4060000000001</v>
       </c>
       <c r="G18">
         <v>74.3</v>
@@ -2757,28 +2757,28 @@
         <v>309.1</v>
       </c>
       <c r="M18">
-        <v>25.1275584</v>
+        <v>26.6980308</v>
       </c>
       <c r="N18">
-        <v>283.9724416</v>
+        <v>282.4019692</v>
       </c>
       <c r="O18">
-        <v>70.99311040000001</v>
+        <v>70.6004923</v>
       </c>
       <c r="P18">
-        <v>212.9793312</v>
+        <v>211.8014769</v>
       </c>
       <c r="Q18">
-        <v>297.2793312</v>
+        <v>296.1014769</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1771158012526331</v>
+        <v>0.1783518310083996</v>
       </c>
       <c r="T18">
-        <v>1.124822753446052</v>
+        <v>1.135410317013881</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.30123496598858</v>
+        <v>11.57763290916572</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1546365197369717</v>
+        <v>0.1542797664217315</v>
       </c>
       <c r="C19">
-        <v>2697.495735247346</v>
+        <v>2677.499536364754</v>
       </c>
       <c r="D19">
-        <v>3138.601735247345</v>
+        <v>3148.923536364754</v>
       </c>
       <c r="E19">
-        <v>282.5060000000001</v>
+        <v>312.8240000000001</v>
       </c>
       <c r="F19">
-        <v>515.4060000000001</v>
+        <v>545.724</v>
       </c>
       <c r="G19">
         <v>74.3</v>
@@ -2839,28 +2839,28 @@
         <v>309.1</v>
       </c>
       <c r="M19">
-        <v>26.6980308</v>
+        <v>28.2685032</v>
       </c>
       <c r="N19">
-        <v>282.4019692</v>
+        <v>280.8314968</v>
       </c>
       <c r="O19">
-        <v>70.6004923</v>
+        <v>70.20787420000001</v>
       </c>
       <c r="P19">
-        <v>211.8014769</v>
+        <v>210.6236226</v>
       </c>
       <c r="Q19">
-        <v>296.1014769</v>
+        <v>294.9236226</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1783518310083996</v>
+        <v>0.1796180078313799</v>
       </c>
       <c r="T19">
-        <v>1.135410317013881</v>
+        <v>1.14625611383946</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.57763290916572</v>
+        <v>10.93443108087874</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1542797664217315</v>
+        <v>0.1539230131064914</v>
       </c>
       <c r="C20">
-        <v>2677.499536364753</v>
+        <v>2657.571451321427</v>
       </c>
       <c r="D20">
-        <v>3148.923536364753</v>
+        <v>3159.313451321426</v>
       </c>
       <c r="E20">
-        <v>312.8240000000001</v>
+        <v>343.1420000000001</v>
       </c>
       <c r="F20">
-        <v>545.724</v>
+        <v>576.042</v>
       </c>
       <c r="G20">
         <v>74.3</v>
@@ -2921,28 +2921,28 @@
         <v>309.1</v>
       </c>
       <c r="M20">
-        <v>28.2685032</v>
+        <v>29.8389756</v>
       </c>
       <c r="N20">
-        <v>280.8314968</v>
+        <v>279.2610244</v>
       </c>
       <c r="O20">
-        <v>70.20787420000001</v>
+        <v>69.8152561</v>
       </c>
       <c r="P20">
-        <v>210.6236226</v>
+        <v>209.4457683</v>
       </c>
       <c r="Q20">
-        <v>294.9236226</v>
+        <v>293.7457683</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1796180078313799</v>
+        <v>0.180915448279619</v>
       </c>
       <c r="T20">
-        <v>1.14625611383946</v>
+        <v>1.157369708117524</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.93443108087874</v>
+        <v>10.35893470820091</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1539230131064914</v>
+        <v>0.1535662597912513</v>
       </c>
       <c r="C21">
-        <v>2657.571451321427</v>
+        <v>2637.712156576903</v>
       </c>
       <c r="D21">
-        <v>3159.313451321426</v>
+        <v>3169.772156576902</v>
       </c>
       <c r="E21">
-        <v>343.1420000000001</v>
+        <v>373.46</v>
       </c>
       <c r="F21">
-        <v>576.042</v>
+        <v>606.36</v>
       </c>
       <c r="G21">
         <v>74.3</v>
@@ -3003,28 +3003,28 @@
         <v>309.1</v>
       </c>
       <c r="M21">
-        <v>29.8389756</v>
+        <v>31.409448</v>
       </c>
       <c r="N21">
-        <v>279.2610244</v>
+        <v>277.690552</v>
       </c>
       <c r="O21">
-        <v>69.8152561</v>
+        <v>69.42263800000001</v>
       </c>
       <c r="P21">
-        <v>209.4457683</v>
+        <v>208.267914</v>
       </c>
       <c r="Q21">
-        <v>293.7457683</v>
+        <v>292.567914</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.180915448279619</v>
+        <v>0.1822453247390641</v>
       </c>
       <c r="T21">
-        <v>1.157369708117524</v>
+        <v>1.168761142252539</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.35893470820091</v>
+        <v>9.840987972790863</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1535662597912513</v>
+        <v>0.1534772564760111</v>
       </c>
       <c r="C22">
-        <v>2637.712156576903</v>
+        <v>2610.014210613606</v>
       </c>
       <c r="D22">
-        <v>3169.772156576902</v>
+        <v>3172.392210613606</v>
       </c>
       <c r="E22">
-        <v>373.46</v>
+        <v>403.7780000000001</v>
       </c>
       <c r="F22">
-        <v>606.36</v>
+        <v>636.6780000000001</v>
       </c>
       <c r="G22">
         <v>74.3</v>
@@ -3085,45 +3085,45 @@
         <v>309.1</v>
       </c>
       <c r="M22">
-        <v>31.409448</v>
+        <v>34.062273</v>
       </c>
       <c r="N22">
-        <v>277.690552</v>
+        <v>275.037727</v>
       </c>
       <c r="O22">
-        <v>69.42263800000001</v>
+        <v>68.75943175</v>
       </c>
       <c r="P22">
-        <v>208.267914</v>
+        <v>206.27829525</v>
       </c>
       <c r="Q22">
-        <v>292.567914</v>
+        <v>290.57829525</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1822453247390641</v>
+        <v>0.1836088689569761</v>
       </c>
       <c r="T22">
-        <v>1.168761142252539</v>
+        <v>1.180440967125149</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>9.840987972790863</v>
+        <v>9.074555887682539</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1534772564760111</v>
+        <v>0.153133253160771</v>
       </c>
       <c r="C23">
-        <v>2610.014210613607</v>
+        <v>2589.863734708478</v>
       </c>
       <c r="D23">
-        <v>3172.392210613606</v>
+        <v>3182.559734708478</v>
       </c>
       <c r="E23">
-        <v>403.778</v>
+        <v>434.0960000000001</v>
       </c>
       <c r="F23">
-        <v>636.678</v>
+        <v>666.9960000000001</v>
       </c>
       <c r="G23">
         <v>74.3</v>
@@ -3167,28 +3167,28 @@
         <v>309.1</v>
       </c>
       <c r="M23">
-        <v>34.062273</v>
+        <v>35.68428600000001</v>
       </c>
       <c r="N23">
-        <v>275.037727</v>
+        <v>273.415714</v>
       </c>
       <c r="O23">
-        <v>68.75943175</v>
+        <v>68.35392850000001</v>
       </c>
       <c r="P23">
-        <v>206.27829525</v>
+        <v>205.0617855</v>
       </c>
       <c r="Q23">
-        <v>290.57829525</v>
+        <v>289.3617855</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1836088689569761</v>
+        <v>0.1850073758471423</v>
       </c>
       <c r="T23">
-        <v>1.180440967125149</v>
+        <v>1.192420274686801</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.074555887682541</v>
+        <v>8.662076074606059</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.153133253160771</v>
+        <v>0.1527892498455309</v>
       </c>
       <c r="C24">
-        <v>2589.863734708478</v>
+        <v>2569.778642232086</v>
       </c>
       <c r="D24">
-        <v>3182.559734708478</v>
+        <v>3192.792642232086</v>
       </c>
       <c r="E24">
-        <v>434.0960000000001</v>
+        <v>464.4140000000001</v>
       </c>
       <c r="F24">
-        <v>666.9960000000001</v>
+        <v>697.3140000000001</v>
       </c>
       <c r="G24">
         <v>74.3</v>
@@ -3249,28 +3249,28 @@
         <v>309.1</v>
       </c>
       <c r="M24">
-        <v>35.68428600000001</v>
+        <v>37.306299</v>
       </c>
       <c r="N24">
-        <v>273.415714</v>
+        <v>271.793701</v>
       </c>
       <c r="O24">
-        <v>68.35392850000001</v>
+        <v>67.94842525</v>
       </c>
       <c r="P24">
-        <v>205.0617855</v>
+        <v>203.84527575</v>
       </c>
       <c r="Q24">
-        <v>289.3617855</v>
+        <v>288.1452757499999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1850073758471423</v>
+        <v>0.1864422075915985</v>
       </c>
       <c r="T24">
-        <v>1.192420274686801</v>
+        <v>1.20471073309421</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.662076074606059</v>
+        <v>8.285464071362318</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1527892498455309</v>
+        <v>0.1524452465302907</v>
       </c>
       <c r="C25">
-        <v>2569.778642232086</v>
+        <v>2549.759565902258</v>
       </c>
       <c r="D25">
-        <v>3192.792642232086</v>
+        <v>3203.091565902258</v>
       </c>
       <c r="E25">
-        <v>464.4140000000001</v>
+        <v>494.7320000000001</v>
       </c>
       <c r="F25">
-        <v>697.3140000000001</v>
+        <v>727.6320000000001</v>
       </c>
       <c r="G25">
         <v>74.3</v>
@@ -3331,28 +3331,28 @@
         <v>309.1</v>
       </c>
       <c r="M25">
-        <v>37.306299</v>
+        <v>38.92831200000001</v>
       </c>
       <c r="N25">
-        <v>271.793701</v>
+        <v>270.171688</v>
       </c>
       <c r="O25">
-        <v>67.94842525</v>
+        <v>67.542922</v>
       </c>
       <c r="P25">
-        <v>203.84527575</v>
+        <v>202.628766</v>
       </c>
       <c r="Q25">
-        <v>288.1452757499999</v>
+        <v>286.928766</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1864422075915985</v>
+        <v>0.187914798066172</v>
       </c>
       <c r="T25">
-        <v>1.20471073309421</v>
+        <v>1.217324624617603</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.285464071362318</v>
+        <v>7.940236401722221</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1524452465302907</v>
+        <v>0.1521012432150506</v>
       </c>
       <c r="C26">
-        <v>2549.759565902258</v>
+        <v>2529.807146627019</v>
       </c>
       <c r="D26">
-        <v>3203.091565902258</v>
+        <v>3213.457146627019</v>
       </c>
       <c r="E26">
-        <v>494.7320000000001</v>
+        <v>525.0500000000001</v>
       </c>
       <c r="F26">
-        <v>727.6320000000001</v>
+        <v>757.95</v>
       </c>
       <c r="G26">
         <v>74.3</v>
@@ -3413,28 +3413,28 @@
         <v>309.1</v>
       </c>
       <c r="M26">
-        <v>38.92831200000001</v>
+        <v>40.550325</v>
       </c>
       <c r="N26">
-        <v>270.171688</v>
+        <v>268.549675</v>
       </c>
       <c r="O26">
-        <v>67.542922</v>
+        <v>67.13741875000001</v>
       </c>
       <c r="P26">
-        <v>202.628766</v>
+        <v>201.41225625</v>
       </c>
       <c r="Q26">
-        <v>286.928766</v>
+        <v>285.71225625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.187914798066172</v>
+        <v>0.1894266576200674</v>
       </c>
       <c r="T26">
-        <v>1.217324624617603</v>
+        <v>1.23027488658162</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.940236401722221</v>
+        <v>7.622626945653334</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1521012432150506</v>
+        <v>0.1519132398998104</v>
       </c>
       <c r="C27">
-        <v>2529.807146627019</v>
+        <v>2505.182504001825</v>
       </c>
       <c r="D27">
-        <v>3213.457146627019</v>
+        <v>3219.150504001825</v>
       </c>
       <c r="E27">
-        <v>525.0500000000001</v>
+        <v>555.3680000000001</v>
       </c>
       <c r="F27">
-        <v>757.95</v>
+        <v>788.268</v>
       </c>
       <c r="G27">
         <v>74.3</v>
@@ -3495,45 +3495,45 @@
         <v>309.1</v>
       </c>
       <c r="M27">
-        <v>40.550325</v>
+        <v>42.8029524</v>
       </c>
       <c r="N27">
-        <v>268.549675</v>
+        <v>266.2970476</v>
       </c>
       <c r="O27">
-        <v>67.13741875000001</v>
+        <v>66.57426190000001</v>
       </c>
       <c r="P27">
-        <v>201.41225625</v>
+        <v>199.7227857</v>
       </c>
       <c r="Q27">
-        <v>285.71225625</v>
+        <v>284.0227857</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1894266576200674</v>
+        <v>0.1909793782429871</v>
       </c>
       <c r="T27">
-        <v>1.23027488658162</v>
+        <v>1.243575155625745</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.622626945653334</v>
+        <v>7.221464470754593</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1519132398998104</v>
+        <v>0.1515752365845703</v>
       </c>
       <c r="C28">
-        <v>2505.182504001825</v>
+        <v>2485.151255208848</v>
       </c>
       <c r="D28">
-        <v>3219.150504001825</v>
+        <v>3229.437255208848</v>
       </c>
       <c r="E28">
-        <v>555.3680000000001</v>
+        <v>585.6860000000001</v>
       </c>
       <c r="F28">
-        <v>788.268</v>
+        <v>818.5860000000001</v>
       </c>
       <c r="G28">
         <v>74.3</v>
@@ -3577,28 +3577,28 @@
         <v>309.1</v>
       </c>
       <c r="M28">
-        <v>42.8029524</v>
+        <v>44.44921980000001</v>
       </c>
       <c r="N28">
-        <v>266.2970476</v>
+        <v>264.6507802</v>
       </c>
       <c r="O28">
-        <v>66.57426190000001</v>
+        <v>66.16269505</v>
       </c>
       <c r="P28">
-        <v>199.7227857</v>
+        <v>198.48808515</v>
       </c>
       <c r="Q28">
-        <v>284.0227857</v>
+        <v>282.7880851499999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1909793782429871</v>
+        <v>0.1925746391569456</v>
       </c>
       <c r="T28">
-        <v>1.243575155625745</v>
+        <v>1.257239815602587</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.221464470754593</v>
+        <v>6.954002823689605</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1515752365845703</v>
+        <v>0.1512372332693302</v>
       </c>
       <c r="C29">
-        <v>2485.151255208848</v>
+        <v>2465.185959512387</v>
       </c>
       <c r="D29">
-        <v>3229.437255208848</v>
+        <v>3239.789959512387</v>
       </c>
       <c r="E29">
-        <v>585.6860000000001</v>
+        <v>616.0040000000001</v>
       </c>
       <c r="F29">
-        <v>818.5860000000001</v>
+        <v>848.9040000000001</v>
       </c>
       <c r="G29">
         <v>74.3</v>
@@ -3659,28 +3659,28 @@
         <v>309.1</v>
       </c>
       <c r="M29">
-        <v>44.44921980000001</v>
+        <v>46.09548720000001</v>
       </c>
       <c r="N29">
-        <v>264.6507802</v>
+        <v>263.0045128</v>
       </c>
       <c r="O29">
-        <v>66.16269505</v>
+        <v>65.75112820000001</v>
       </c>
       <c r="P29">
-        <v>198.48808515</v>
+        <v>197.2533846</v>
       </c>
       <c r="Q29">
-        <v>282.7880851499999</v>
+        <v>281.5533846</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1925746391569456</v>
+        <v>0.1942142128740697</v>
       </c>
       <c r="T29">
-        <v>1.257239815602587</v>
+        <v>1.271284049467674</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.954002823689605</v>
+        <v>6.705645579986407</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1512372332693302</v>
+        <v>0.15089922995409</v>
       </c>
       <c r="C30">
-        <v>2465.185959512387</v>
+        <v>2445.287253235806</v>
       </c>
       <c r="D30">
-        <v>3239.789959512387</v>
+        <v>3250.209253235807</v>
       </c>
       <c r="E30">
-        <v>616.0040000000001</v>
+        <v>646.3220000000002</v>
       </c>
       <c r="F30">
-        <v>848.9040000000001</v>
+        <v>879.2220000000002</v>
       </c>
       <c r="G30">
         <v>74.3</v>
@@ -3741,28 +3741,28 @@
         <v>309.1</v>
       </c>
       <c r="M30">
-        <v>46.09548720000001</v>
+        <v>47.74175460000001</v>
       </c>
       <c r="N30">
-        <v>263.0045128</v>
+        <v>261.3582454</v>
       </c>
       <c r="O30">
-        <v>65.75112820000001</v>
+        <v>65.33956135</v>
       </c>
       <c r="P30">
-        <v>197.2533846</v>
+        <v>196.01868405</v>
       </c>
       <c r="Q30">
-        <v>281.5533846</v>
+        <v>280.3186840499999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1942142128740697</v>
+        <v>0.195899971766324</v>
       </c>
       <c r="T30">
-        <v>1.271284049467674</v>
+        <v>1.285723895554312</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.705645579986407</v>
+        <v>6.474416422055839</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.15089922995409</v>
+        <v>0.1505612266388499</v>
       </c>
       <c r="C31">
-        <v>2445.287253235807</v>
+        <v>2425.455780914651</v>
       </c>
       <c r="D31">
-        <v>3250.209253235807</v>
+        <v>3260.695780914651</v>
       </c>
       <c r="E31">
-        <v>646.322</v>
+        <v>676.6400000000001</v>
       </c>
       <c r="F31">
-        <v>879.222</v>
+        <v>909.5400000000001</v>
       </c>
       <c r="G31">
         <v>74.3</v>
@@ -3823,28 +3823,28 @@
         <v>309.1</v>
       </c>
       <c r="M31">
-        <v>47.7417546</v>
+        <v>49.38802200000001</v>
       </c>
       <c r="N31">
-        <v>261.3582454</v>
+        <v>259.711978</v>
       </c>
       <c r="O31">
-        <v>65.33956135000001</v>
+        <v>64.92799450000001</v>
       </c>
       <c r="P31">
-        <v>196.01868405</v>
+        <v>194.7839835</v>
       </c>
       <c r="Q31">
-        <v>280.31868405</v>
+        <v>279.0839835</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.195899971766324</v>
+        <v>0.197633895198357</v>
       </c>
       <c r="T31">
-        <v>1.285723895554312</v>
+        <v>1.300576308671998</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.474416422055842</v>
+        <v>6.258602541320647</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1505612266388499</v>
+        <v>0.1504557233236097</v>
       </c>
       <c r="C32">
-        <v>2425.455780914651</v>
+        <v>2398.424884609995</v>
       </c>
       <c r="D32">
-        <v>3260.695780914651</v>
+        <v>3263.982884609995</v>
       </c>
       <c r="E32">
-        <v>676.6400000000001</v>
+        <v>706.9580000000001</v>
       </c>
       <c r="F32">
-        <v>909.5400000000001</v>
+        <v>939.8580000000001</v>
       </c>
       <c r="G32">
         <v>74.3</v>
@@ -3905,45 +3905,45 @@
         <v>309.1</v>
       </c>
       <c r="M32">
-        <v>49.38802200000001</v>
+        <v>51.97414740000001</v>
       </c>
       <c r="N32">
-        <v>259.711978</v>
+        <v>257.1258526</v>
       </c>
       <c r="O32">
-        <v>64.92799450000001</v>
+        <v>64.28146315000001</v>
       </c>
       <c r="P32">
-        <v>194.7839835</v>
+        <v>192.84438945</v>
       </c>
       <c r="Q32">
-        <v>279.0839835</v>
+        <v>277.1443894499999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.197633895198357</v>
+        <v>0.1994180772805939</v>
       </c>
       <c r="T32">
-        <v>1.300576308671998</v>
+        <v>1.315859226517732</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.258602541320647</v>
+        <v>5.947187504994069</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1504557233236097</v>
+        <v>0.1501252200083696</v>
       </c>
       <c r="C33">
-        <v>2398.424884609995</v>
+        <v>2378.447214246147</v>
       </c>
       <c r="D33">
-        <v>3263.982884609995</v>
+        <v>3274.323214246147</v>
       </c>
       <c r="E33">
-        <v>706.9580000000001</v>
+        <v>737.2760000000001</v>
       </c>
       <c r="F33">
-        <v>939.8580000000001</v>
+        <v>970.176</v>
       </c>
       <c r="G33">
         <v>74.3</v>
@@ -3987,28 +3987,28 @@
         <v>309.1</v>
       </c>
       <c r="M33">
-        <v>51.97414740000001</v>
+        <v>53.65073280000001</v>
       </c>
       <c r="N33">
-        <v>257.1258526</v>
+        <v>255.4492672</v>
       </c>
       <c r="O33">
-        <v>64.28146315000001</v>
+        <v>63.8623168</v>
       </c>
       <c r="P33">
-        <v>192.84438945</v>
+        <v>191.5869504</v>
       </c>
       <c r="Q33">
-        <v>277.1443894499999</v>
+        <v>275.8869503999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1994180772805939</v>
+        <v>0.2012547353064259</v>
       </c>
       <c r="T33">
-        <v>1.315859226517732</v>
+        <v>1.331591641947165</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.947187504994069</v>
+        <v>5.761337895463004</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1501252200083696</v>
+        <v>0.1497947166931295</v>
       </c>
       <c r="C34">
-        <v>2378.447214246147</v>
+        <v>2358.535268629365</v>
       </c>
       <c r="D34">
-        <v>3274.323214246147</v>
+        <v>3284.729268629365</v>
       </c>
       <c r="E34">
-        <v>737.2760000000001</v>
+        <v>767.5940000000002</v>
       </c>
       <c r="F34">
-        <v>970.176</v>
+        <v>1000.494</v>
       </c>
       <c r="G34">
         <v>74.3</v>
@@ -4069,28 +4069,28 @@
         <v>309.1</v>
       </c>
       <c r="M34">
-        <v>53.65073280000001</v>
+        <v>55.32731820000001</v>
       </c>
       <c r="N34">
-        <v>255.4492672</v>
+        <v>253.7726818</v>
       </c>
       <c r="O34">
-        <v>63.8623168</v>
+        <v>63.44317045</v>
       </c>
       <c r="P34">
-        <v>191.5869504</v>
+        <v>190.32951135</v>
       </c>
       <c r="Q34">
-        <v>275.8869503999999</v>
+        <v>274.62951135</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2012547353064259</v>
+        <v>0.2031462189449694</v>
       </c>
       <c r="T34">
-        <v>1.331591641947165</v>
+        <v>1.347793681717774</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.761337895463004</v>
+        <v>5.586751898630792</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1497947166931295</v>
+        <v>0.1494642133778893</v>
       </c>
       <c r="C35">
-        <v>2358.535268629365</v>
+        <v>2338.689676392602</v>
       </c>
       <c r="D35">
-        <v>3284.729268629365</v>
+        <v>3295.201676392601</v>
       </c>
       <c r="E35">
-        <v>767.5940000000002</v>
+        <v>797.9120000000001</v>
       </c>
       <c r="F35">
-        <v>1000.494</v>
+        <v>1030.812</v>
       </c>
       <c r="G35">
         <v>74.3</v>
@@ -4151,28 +4151,28 @@
         <v>309.1</v>
       </c>
       <c r="M35">
-        <v>55.32731820000001</v>
+        <v>57.00390360000001</v>
       </c>
       <c r="N35">
-        <v>253.7726818</v>
+        <v>252.0960964</v>
       </c>
       <c r="O35">
-        <v>63.44317045</v>
+        <v>63.02402410000001</v>
       </c>
       <c r="P35">
-        <v>190.32951135</v>
+        <v>189.0720723</v>
       </c>
       <c r="Q35">
-        <v>274.62951135</v>
+        <v>273.3720723</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2031462189449694</v>
+        <v>0.2050950202695294</v>
       </c>
       <c r="T35">
-        <v>1.347793681717774</v>
+        <v>1.364486692390524</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.586751898630792</v>
+        <v>5.422435666318122</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1494642133778893</v>
+        <v>0.1491337100626492</v>
       </c>
       <c r="C36">
-        <v>2338.689676392602</v>
+        <v>2318.911074211302</v>
       </c>
       <c r="D36">
-        <v>3295.201676392601</v>
+        <v>3305.741074211302</v>
       </c>
       <c r="E36">
-        <v>797.9120000000001</v>
+        <v>828.2300000000001</v>
       </c>
       <c r="F36">
-        <v>1030.812</v>
+        <v>1061.13</v>
       </c>
       <c r="G36">
         <v>74.3</v>
@@ -4233,28 +4233,28 @@
         <v>309.1</v>
       </c>
       <c r="M36">
-        <v>57.00390360000001</v>
+        <v>58.68048900000001</v>
       </c>
       <c r="N36">
-        <v>252.0960964</v>
+        <v>250.419511</v>
       </c>
       <c r="O36">
-        <v>63.02402410000001</v>
+        <v>62.60487775</v>
       </c>
       <c r="P36">
-        <v>189.0720723</v>
+        <v>187.81463325</v>
       </c>
       <c r="Q36">
-        <v>273.3720723</v>
+        <v>272.1146332499999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2050950202695294</v>
+        <v>0.207103784711768</v>
       </c>
       <c r="T36">
-        <v>1.364486692390524</v>
+        <v>1.381693334160896</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.422435666318122</v>
+        <v>5.267508932994747</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1491337100626492</v>
+        <v>0.1488032067474091</v>
       </c>
       <c r="C37">
-        <v>2318.911074211302</v>
+        <v>2299.200106932444</v>
       </c>
       <c r="D37">
-        <v>3305.741074211302</v>
+        <v>3316.348106932444</v>
       </c>
       <c r="E37">
-        <v>828.2300000000001</v>
+        <v>858.5480000000001</v>
       </c>
       <c r="F37">
-        <v>1061.13</v>
+        <v>1091.448</v>
       </c>
       <c r="G37">
         <v>74.3</v>
@@ -4315,28 +4315,28 @@
         <v>309.1</v>
       </c>
       <c r="M37">
-        <v>58.68048900000001</v>
+        <v>60.35707440000001</v>
       </c>
       <c r="N37">
-        <v>250.419511</v>
+        <v>248.7429256</v>
       </c>
       <c r="O37">
-        <v>62.60487775</v>
+        <v>62.1857314</v>
       </c>
       <c r="P37">
-        <v>187.81463325</v>
+        <v>186.5571942</v>
       </c>
       <c r="Q37">
-        <v>272.1146332499999</v>
+        <v>270.8571942</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.207103784711768</v>
+        <v>0.2091753230428267</v>
       </c>
       <c r="T37">
-        <v>1.381693334160896</v>
+        <v>1.399437683486592</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.267508932994747</v>
+        <v>5.121189240411559</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1488032067474091</v>
+        <v>0.148472703432169</v>
       </c>
       <c r="C38">
-        <v>2299.200106932443</v>
+        <v>2279.557427706048</v>
       </c>
       <c r="D38">
-        <v>3316.348106932443</v>
+        <v>3327.023427706048</v>
       </c>
       <c r="E38">
-        <v>858.5480000000001</v>
+        <v>888.8660000000001</v>
       </c>
       <c r="F38">
-        <v>1091.448</v>
+        <v>1121.766</v>
       </c>
       <c r="G38">
         <v>74.3</v>
@@ -4397,28 +4397,28 @@
         <v>309.1</v>
       </c>
       <c r="M38">
-        <v>60.35707440000001</v>
+        <v>62.03365980000001</v>
       </c>
       <c r="N38">
-        <v>248.7429256</v>
+        <v>247.0663402</v>
       </c>
       <c r="O38">
-        <v>62.1857314</v>
+        <v>61.76658505</v>
       </c>
       <c r="P38">
-        <v>186.5571942</v>
+        <v>185.29975515</v>
       </c>
       <c r="Q38">
-        <v>270.8571942</v>
+        <v>269.59975515</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2091753230428267</v>
+        <v>0.2113126244955063</v>
       </c>
       <c r="T38">
-        <v>1.399437683486592</v>
+        <v>1.417745345489295</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.121189240411559</v>
+        <v>4.982778720400436</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.148472703432169</v>
+        <v>0.1481422001169288</v>
       </c>
       <c r="C39">
-        <v>2279.557427706048</v>
+        <v>2259.983698119251</v>
       </c>
       <c r="D39">
-        <v>3327.023427706048</v>
+        <v>3337.767698119251</v>
       </c>
       <c r="E39">
-        <v>888.8660000000001</v>
+        <v>919.1840000000001</v>
       </c>
       <c r="F39">
-        <v>1121.766</v>
+        <v>1152.084</v>
       </c>
       <c r="G39">
         <v>74.3</v>
@@ -4479,28 +4479,28 @@
         <v>309.1</v>
       </c>
       <c r="M39">
-        <v>62.03365980000001</v>
+        <v>63.7102452</v>
       </c>
       <c r="N39">
-        <v>247.0663402</v>
+        <v>245.3897548</v>
       </c>
       <c r="O39">
-        <v>61.76658505</v>
+        <v>61.3474387</v>
       </c>
       <c r="P39">
-        <v>185.29975515</v>
+        <v>184.0423161</v>
       </c>
       <c r="Q39">
-        <v>269.59975515</v>
+        <v>268.3423160999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2113126244955063</v>
+        <v>0.2135188711563368</v>
       </c>
       <c r="T39">
-        <v>1.417745345489295</v>
+        <v>1.43664357723402</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.982778720400436</v>
+        <v>4.851652964600426</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1481422001169288</v>
+        <v>0.1478116968016887</v>
       </c>
       <c r="C40">
-        <v>2259.983698119251</v>
+        <v>2240.479588332982</v>
       </c>
       <c r="D40">
-        <v>3337.767698119251</v>
+        <v>3348.581588332982</v>
       </c>
       <c r="E40">
-        <v>919.1840000000001</v>
+        <v>949.5020000000001</v>
       </c>
       <c r="F40">
-        <v>1152.084</v>
+        <v>1182.402</v>
       </c>
       <c r="G40">
         <v>74.3</v>
@@ -4561,28 +4561,28 @@
         <v>309.1</v>
       </c>
       <c r="M40">
-        <v>63.7102452</v>
+        <v>65.38683060000001</v>
       </c>
       <c r="N40">
-        <v>245.3897548</v>
+        <v>243.7131694</v>
       </c>
       <c r="O40">
-        <v>61.3474387</v>
+        <v>60.92829235000001</v>
       </c>
       <c r="P40">
-        <v>184.0423161</v>
+        <v>182.78487705</v>
       </c>
       <c r="Q40">
-        <v>268.3423160999999</v>
+        <v>267.08487705</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2135188711563368</v>
+        <v>0.2157974537732601</v>
       </c>
       <c r="T40">
-        <v>1.43664357723402</v>
+        <v>1.456161423134311</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.851652964600426</v>
+        <v>4.727251606533747</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1478116968016887</v>
+        <v>0.1474811934864485</v>
       </c>
       <c r="C41">
-        <v>2240.479588332982</v>
+        <v>2221.0457772213</v>
       </c>
       <c r="D41">
-        <v>3348.581588332982</v>
+        <v>3359.4657772213</v>
       </c>
       <c r="E41">
-        <v>949.5020000000001</v>
+        <v>979.8200000000001</v>
       </c>
       <c r="F41">
-        <v>1182.402</v>
+        <v>1212.72</v>
       </c>
       <c r="G41">
         <v>74.3</v>
@@ -4643,28 +4643,28 @@
         <v>309.1</v>
       </c>
       <c r="M41">
-        <v>65.38683060000001</v>
+        <v>67.063416</v>
       </c>
       <c r="N41">
-        <v>243.7131694</v>
+        <v>242.036584</v>
       </c>
       <c r="O41">
-        <v>60.92829235000001</v>
+        <v>60.509146</v>
       </c>
       <c r="P41">
-        <v>182.78487705</v>
+        <v>181.527438</v>
       </c>
       <c r="Q41">
-        <v>267.08487705</v>
+        <v>265.827438</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2157974537732601</v>
+        <v>0.2181519891440809</v>
       </c>
       <c r="T41">
-        <v>1.456161423134311</v>
+        <v>1.476329863897944</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.727251606533747</v>
+        <v>4.609070316370404</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1474811934864485</v>
+        <v>0.1479194401712084</v>
       </c>
       <c r="C42">
-        <v>2221.0457772213</v>
+        <v>2176.310593412192</v>
       </c>
       <c r="D42">
-        <v>3359.4657772213</v>
+        <v>3345.048593412192</v>
       </c>
       <c r="E42">
-        <v>979.8200000000001</v>
+        <v>1010.138</v>
       </c>
       <c r="F42">
-        <v>1212.72</v>
+        <v>1243.038</v>
       </c>
       <c r="G42">
         <v>74.3</v>
@@ -4725,45 +4725,45 @@
         <v>309.1</v>
       </c>
       <c r="M42">
-        <v>67.063416</v>
+        <v>71.84759640000001</v>
       </c>
       <c r="N42">
-        <v>242.036584</v>
+        <v>237.2524036</v>
       </c>
       <c r="O42">
-        <v>60.509146</v>
+        <v>59.3131009</v>
       </c>
       <c r="P42">
-        <v>181.527438</v>
+        <v>177.9393027</v>
       </c>
       <c r="Q42">
-        <v>265.827438</v>
+        <v>262.2393026999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2181519891440809</v>
+        <v>0.2205863392732346</v>
       </c>
       <c r="T42">
-        <v>1.476329863897944</v>
+        <v>1.497181980619666</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.609070316370404</v>
+        <v>4.302162013592426</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1479194401712084</v>
+        <v>0.1476076868559683</v>
       </c>
       <c r="C43">
-        <v>2176.310593412192</v>
+        <v>2156.235729474314</v>
       </c>
       <c r="D43">
-        <v>3345.048593412192</v>
+        <v>3355.291729474314</v>
       </c>
       <c r="E43">
-        <v>1010.138</v>
+        <v>1040.456</v>
       </c>
       <c r="F43">
-        <v>1243.038</v>
+        <v>1273.356</v>
       </c>
       <c r="G43">
         <v>74.3</v>
@@ -4807,28 +4807,28 @@
         <v>309.1</v>
       </c>
       <c r="M43">
-        <v>71.84759640000001</v>
+        <v>73.59997680000002</v>
       </c>
       <c r="N43">
-        <v>237.2524036</v>
+        <v>235.5000232</v>
       </c>
       <c r="O43">
-        <v>59.3131009</v>
+        <v>58.8750058</v>
       </c>
       <c r="P43">
-        <v>177.9393027</v>
+        <v>176.6250174</v>
       </c>
       <c r="Q43">
-        <v>262.2393026999999</v>
+        <v>260.9250173999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2205863392732346</v>
+        <v>0.2231046325102901</v>
       </c>
       <c r="T43">
-        <v>1.497181980619666</v>
+        <v>1.518753135849034</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.302162013592426</v>
+        <v>4.199729584697367</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1476076868559683</v>
+        <v>0.1472959335407281</v>
       </c>
       <c r="C44">
-        <v>2156.235729474313</v>
+        <v>2136.223790848111</v>
       </c>
       <c r="D44">
-        <v>3355.291729474313</v>
+        <v>3365.59779084811</v>
       </c>
       <c r="E44">
-        <v>1040.456</v>
+        <v>1070.774</v>
       </c>
       <c r="F44">
-        <v>1273.356</v>
+        <v>1303.674</v>
       </c>
       <c r="G44">
         <v>74.3</v>
@@ -4889,28 +4889,28 @@
         <v>309.1</v>
       </c>
       <c r="M44">
-        <v>73.59997680000001</v>
+        <v>75.3523572</v>
       </c>
       <c r="N44">
-        <v>235.5000232</v>
+        <v>233.7476428</v>
       </c>
       <c r="O44">
-        <v>58.8750058</v>
+        <v>58.43691070000001</v>
       </c>
       <c r="P44">
-        <v>176.6250174</v>
+        <v>175.3107321</v>
       </c>
       <c r="Q44">
-        <v>260.9250174</v>
+        <v>259.6107321</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2231046325102901</v>
+        <v>0.2257112869135581</v>
       </c>
       <c r="T44">
-        <v>1.518753135849034</v>
+        <v>1.541081173718029</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.199729584697369</v>
+        <v>4.102061454820687</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1472959335407281</v>
+        <v>0.146984180225488</v>
       </c>
       <c r="C45">
-        <v>2136.223790848111</v>
+        <v>2116.275359161294</v>
       </c>
       <c r="D45">
-        <v>3365.59779084811</v>
+        <v>3375.967359161294</v>
       </c>
       <c r="E45">
-        <v>1070.774</v>
+        <v>1101.092</v>
       </c>
       <c r="F45">
-        <v>1303.674</v>
+        <v>1333.992</v>
       </c>
       <c r="G45">
         <v>74.3</v>
@@ -4971,28 +4971,28 @@
         <v>309.1</v>
       </c>
       <c r="M45">
-        <v>75.3523572</v>
+        <v>77.10473760000002</v>
       </c>
       <c r="N45">
-        <v>233.7476428</v>
+        <v>231.9952624</v>
       </c>
       <c r="O45">
-        <v>58.43691070000001</v>
+        <v>57.9988156</v>
       </c>
       <c r="P45">
-        <v>175.3107321</v>
+        <v>173.9964468</v>
       </c>
       <c r="Q45">
-        <v>259.6107321</v>
+        <v>258.2964468</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2257112869135581</v>
+        <v>0.2284110361169429</v>
       </c>
       <c r="T45">
-        <v>1.541081173718029</v>
+        <v>1.564206641510917</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.102061454820687</v>
+        <v>4.008832785392942</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.146984180225488</v>
+        <v>0.1478536769102479</v>
       </c>
       <c r="C46">
-        <v>2116.275359161294</v>
+        <v>2057.194138515852</v>
       </c>
       <c r="D46">
-        <v>3375.967359161294</v>
+        <v>3347.204138515851</v>
       </c>
       <c r="E46">
-        <v>1101.092</v>
+        <v>1131.41</v>
       </c>
       <c r="F46">
-        <v>1333.992</v>
+        <v>1364.31</v>
       </c>
       <c r="G46">
         <v>74.3</v>
@@ -5053,45 +5053,45 @@
         <v>309.1</v>
       </c>
       <c r="M46">
-        <v>77.10473760000002</v>
+        <v>83.632203</v>
       </c>
       <c r="N46">
-        <v>231.9952624</v>
+        <v>225.467797</v>
       </c>
       <c r="O46">
-        <v>57.9988156</v>
+        <v>56.36694925</v>
       </c>
       <c r="P46">
-        <v>173.9964468</v>
+        <v>169.10084775</v>
       </c>
       <c r="Q46">
-        <v>258.2964468</v>
+        <v>253.40084775</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2284110361169429</v>
+        <v>0.2312089580186325</v>
       </c>
       <c r="T46">
-        <v>1.564206641510917</v>
+        <v>1.588173035405364</v>
       </c>
       <c r="U46">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.008832785392942</v>
+        <v>3.695944730763579</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1478536769102479</v>
+        <v>0.1475681735950077</v>
       </c>
       <c r="C47">
-        <v>2057.194138515852</v>
+        <v>2036.266479764725</v>
       </c>
       <c r="D47">
-        <v>3347.204138515851</v>
+        <v>3356.594479764725</v>
       </c>
       <c r="E47">
-        <v>1131.41</v>
+        <v>1161.728</v>
       </c>
       <c r="F47">
-        <v>1364.31</v>
+        <v>1394.628</v>
       </c>
       <c r="G47">
         <v>74.3</v>
@@ -5135,28 +5135,28 @@
         <v>309.1</v>
       </c>
       <c r="M47">
-        <v>83.632203</v>
+        <v>85.4906964</v>
       </c>
       <c r="N47">
-        <v>225.467797</v>
+        <v>223.6093036</v>
       </c>
       <c r="O47">
-        <v>56.36694925</v>
+        <v>55.90232590000001</v>
       </c>
       <c r="P47">
-        <v>169.10084775</v>
+        <v>167.7069777</v>
       </c>
       <c r="Q47">
-        <v>253.40084775</v>
+        <v>252.0069777</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2312089580186325</v>
+        <v>0.2341105066574217</v>
       </c>
       <c r="T47">
-        <v>1.588173035405364</v>
+        <v>1.613027073518124</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.695944730763579</v>
+        <v>3.615598106181762</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1475681735950077</v>
+        <v>0.1472826702797676</v>
       </c>
       <c r="C48">
-        <v>2036.266479764725</v>
+        <v>2015.391657099808</v>
       </c>
       <c r="D48">
-        <v>3356.594479764725</v>
+        <v>3366.037657099808</v>
       </c>
       <c r="E48">
-        <v>1161.728</v>
+        <v>1192.046</v>
       </c>
       <c r="F48">
-        <v>1394.628</v>
+        <v>1424.946</v>
       </c>
       <c r="G48">
         <v>74.3</v>
@@ -5217,28 +5217,28 @@
         <v>309.1</v>
       </c>
       <c r="M48">
-        <v>85.4906964</v>
+        <v>87.3491898</v>
       </c>
       <c r="N48">
-        <v>223.6093036</v>
+        <v>221.7508102</v>
       </c>
       <c r="O48">
-        <v>55.90232590000001</v>
+        <v>55.43770255</v>
       </c>
       <c r="P48">
-        <v>167.7069777</v>
+        <v>166.31310765</v>
       </c>
       <c r="Q48">
-        <v>252.0069777</v>
+        <v>250.61310765</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2341105066574217</v>
+        <v>0.2371215476976747</v>
       </c>
       <c r="T48">
-        <v>1.613027073518124</v>
+        <v>1.638818999861554</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.615598106181762</v>
+        <v>3.538670486901299</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1472826702797676</v>
+        <v>0.1480051669645275</v>
       </c>
       <c r="C49">
-        <v>2015.391657099808</v>
+        <v>1961.278861589366</v>
       </c>
       <c r="D49">
-        <v>3366.037657099808</v>
+        <v>3342.242861589365</v>
       </c>
       <c r="E49">
-        <v>1192.046</v>
+        <v>1222.364</v>
       </c>
       <c r="F49">
-        <v>1424.946</v>
+        <v>1455.264</v>
       </c>
       <c r="G49">
         <v>74.3</v>
@@ -5299,45 +5299,45 @@
         <v>309.1</v>
       </c>
       <c r="M49">
-        <v>87.3491898</v>
+        <v>93.28242240000002</v>
       </c>
       <c r="N49">
-        <v>221.7508102</v>
+        <v>215.8175776</v>
       </c>
       <c r="O49">
-        <v>55.43770255</v>
+        <v>53.9543944</v>
       </c>
       <c r="P49">
-        <v>166.31310765</v>
+        <v>161.8631832</v>
       </c>
       <c r="Q49">
-        <v>250.61310765</v>
+        <v>246.1631831999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2371215476976747</v>
+        <v>0.2402483980087067</v>
       </c>
       <c r="T49">
-        <v>1.638818999861554</v>
+        <v>1.665602923372039</v>
       </c>
       <c r="U49">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.538670486901299</v>
+        <v>3.31359319416645</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1480051669645275</v>
+        <v>0.1477406636492873</v>
       </c>
       <c r="C50">
-        <v>1961.278861589366</v>
+        <v>1939.632909480574</v>
       </c>
       <c r="D50">
-        <v>3342.242861589365</v>
+        <v>3350.914909480573</v>
       </c>
       <c r="E50">
-        <v>1222.364</v>
+        <v>1252.682</v>
       </c>
       <c r="F50">
-        <v>1455.264</v>
+        <v>1485.582</v>
       </c>
       <c r="G50">
         <v>74.3</v>
@@ -5381,28 +5381,28 @@
         <v>309.1</v>
       </c>
       <c r="M50">
-        <v>93.28242240000002</v>
+        <v>95.22580620000001</v>
       </c>
       <c r="N50">
-        <v>215.8175776</v>
+        <v>213.8741938</v>
       </c>
       <c r="O50">
-        <v>53.9543944</v>
+        <v>53.46854845</v>
       </c>
       <c r="P50">
-        <v>161.8631832</v>
+        <v>160.40564535</v>
       </c>
       <c r="Q50">
-        <v>246.1631831999999</v>
+        <v>244.7056453499999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2402483980087067</v>
+        <v>0.2434978699005634</v>
       </c>
       <c r="T50">
-        <v>1.665602923372039</v>
+        <v>1.693437196824112</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.31359319416645</v>
+        <v>3.245968843265094</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1477406636492873</v>
+        <v>0.1474761603340472</v>
       </c>
       <c r="C51">
-        <v>1939.632909480574</v>
+        <v>1918.032076806063</v>
       </c>
       <c r="D51">
-        <v>3350.914909480573</v>
+        <v>3359.632076806063</v>
       </c>
       <c r="E51">
-        <v>1252.682</v>
+        <v>1283</v>
       </c>
       <c r="F51">
-        <v>1485.582</v>
+        <v>1515.9</v>
       </c>
       <c r="G51">
         <v>74.3</v>
@@ -5463,28 +5463,28 @@
         <v>309.1</v>
       </c>
       <c r="M51">
-        <v>95.22580620000001</v>
+        <v>97.16919000000001</v>
       </c>
       <c r="N51">
-        <v>213.8741938</v>
+        <v>211.93081</v>
       </c>
       <c r="O51">
-        <v>53.46854845</v>
+        <v>52.9827025</v>
       </c>
       <c r="P51">
-        <v>160.40564535</v>
+        <v>158.9481075</v>
       </c>
       <c r="Q51">
-        <v>244.7056453499999</v>
+        <v>243.2481074999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2434978699005634</v>
+        <v>0.2468773206680944</v>
       </c>
       <c r="T51">
-        <v>1.693437196824112</v>
+        <v>1.722384841214268</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.245968843265094</v>
+        <v>3.181049466399792</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1474761603340472</v>
+        <v>0.1472116570188071</v>
       </c>
       <c r="C52">
-        <v>1918.032076806063</v>
+        <v>1896.476716609272</v>
       </c>
       <c r="D52">
-        <v>3359.632076806063</v>
+        <v>3368.394716609272</v>
       </c>
       <c r="E52">
-        <v>1283</v>
+        <v>1313.318</v>
       </c>
       <c r="F52">
-        <v>1515.9</v>
+        <v>1546.218</v>
       </c>
       <c r="G52">
         <v>74.3</v>
@@ -5545,28 +5545,28 @@
         <v>309.1</v>
       </c>
       <c r="M52">
-        <v>97.16919000000001</v>
+        <v>99.11257380000001</v>
       </c>
       <c r="N52">
-        <v>211.93081</v>
+        <v>209.9874262</v>
       </c>
       <c r="O52">
-        <v>52.9827025</v>
+        <v>52.49685655</v>
       </c>
       <c r="P52">
-        <v>158.9481075</v>
+        <v>157.49056965</v>
       </c>
       <c r="Q52">
-        <v>243.2481074999999</v>
+        <v>241.79056965</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2468773206680944</v>
+        <v>0.2503947082016471</v>
       </c>
       <c r="T52">
-        <v>1.722384841214268</v>
+        <v>1.752514022110144</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.181049466399792</v>
+        <v>3.118675947450777</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1472116570188071</v>
+        <v>0.1469471537035669</v>
       </c>
       <c r="C53">
-        <v>1896.476716609272</v>
+        <v>1874.967185626519</v>
       </c>
       <c r="D53">
-        <v>3368.394716609272</v>
+        <v>3377.203185626518</v>
       </c>
       <c r="E53">
-        <v>1313.318</v>
+        <v>1343.636</v>
       </c>
       <c r="F53">
-        <v>1546.218</v>
+        <v>1576.536</v>
       </c>
       <c r="G53">
         <v>74.3</v>
@@ -5627,28 +5627,28 @@
         <v>309.1</v>
       </c>
       <c r="M53">
-        <v>99.11257380000001</v>
+        <v>101.0559576</v>
       </c>
       <c r="N53">
-        <v>209.9874262</v>
+        <v>208.0440424</v>
       </c>
       <c r="O53">
-        <v>52.49685655</v>
+        <v>52.01101060000001</v>
       </c>
       <c r="P53">
-        <v>157.49056965</v>
+        <v>156.0330318</v>
       </c>
       <c r="Q53">
-        <v>241.79056965</v>
+        <v>240.3330318</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2503947082016471</v>
+        <v>0.2540586535490977</v>
       </c>
       <c r="T53">
-        <v>1.752514022110144</v>
+        <v>1.783898585543349</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.118675947450777</v>
+        <v>3.0587014099998</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1469471537035669</v>
+        <v>0.1466826503883268</v>
       </c>
       <c r="C54">
-        <v>1874.967185626519</v>
+        <v>1853.503844335416</v>
       </c>
       <c r="D54">
-        <v>3377.203185626518</v>
+        <v>3386.057844335416</v>
       </c>
       <c r="E54">
-        <v>1343.636</v>
+        <v>1373.954</v>
       </c>
       <c r="F54">
-        <v>1576.536</v>
+        <v>1606.854</v>
       </c>
       <c r="G54">
         <v>74.3</v>
@@ -5709,28 +5709,28 @@
         <v>309.1</v>
       </c>
       <c r="M54">
-        <v>101.0559576</v>
+        <v>102.9993414</v>
       </c>
       <c r="N54">
-        <v>208.0440424</v>
+        <v>206.1006586</v>
       </c>
       <c r="O54">
-        <v>52.01101060000001</v>
+        <v>51.52516465</v>
       </c>
       <c r="P54">
-        <v>156.0330318</v>
+        <v>154.57549395</v>
       </c>
       <c r="Q54">
-        <v>240.3330318</v>
+        <v>238.87549395</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2540586535490977</v>
+        <v>0.2578785114645251</v>
       </c>
       <c r="T54">
-        <v>1.783898585543349</v>
+        <v>1.816618662314136</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.0587014099998</v>
+        <v>3.000990062641313</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1466826503883268</v>
+        <v>0.1495771470730866</v>
       </c>
       <c r="C55">
-        <v>1853.503844335416</v>
+        <v>1728.743729850119</v>
       </c>
       <c r="D55">
-        <v>3386.057844335416</v>
+        <v>3291.615729850119</v>
       </c>
       <c r="E55">
-        <v>1373.954</v>
+        <v>1404.272</v>
       </c>
       <c r="F55">
-        <v>1606.854</v>
+        <v>1637.172</v>
       </c>
       <c r="G55">
         <v>74.3</v>
@@ -5791,45 +5791,45 @@
         <v>309.1</v>
       </c>
       <c r="M55">
-        <v>102.9993414</v>
+        <v>117.7126668</v>
       </c>
       <c r="N55">
-        <v>206.1006586</v>
+        <v>191.3873332</v>
       </c>
       <c r="O55">
-        <v>51.52516465</v>
+        <v>47.8468333</v>
       </c>
       <c r="P55">
-        <v>154.57549395</v>
+        <v>143.5404999</v>
       </c>
       <c r="Q55">
-        <v>238.87549395</v>
+        <v>227.8404998999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2578785114645251</v>
+        <v>0.261864450158884</v>
       </c>
       <c r="T55">
-        <v>1.816618662314136</v>
+        <v>1.850761351118437</v>
       </c>
       <c r="U55">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.000990062641313</v>
+        <v>2.625885628138704</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1495771470730866</v>
+        <v>0.1493711437578465</v>
       </c>
       <c r="C56">
-        <v>1728.743729850119</v>
+        <v>1704.972763398682</v>
       </c>
       <c r="D56">
-        <v>3291.615729850119</v>
+        <v>3298.162763398682</v>
       </c>
       <c r="E56">
-        <v>1404.272</v>
+        <v>1434.59</v>
       </c>
       <c r="F56">
-        <v>1637.172</v>
+        <v>1667.49</v>
       </c>
       <c r="G56">
         <v>74.3</v>
@@ -5873,28 +5873,28 @@
         <v>309.1</v>
       </c>
       <c r="M56">
-        <v>117.7126668</v>
+        <v>119.892531</v>
       </c>
       <c r="N56">
-        <v>191.3873332</v>
+        <v>189.207469</v>
       </c>
       <c r="O56">
-        <v>47.8468333</v>
+        <v>47.30186725</v>
       </c>
       <c r="P56">
-        <v>143.5404999</v>
+        <v>141.90560175</v>
       </c>
       <c r="Q56">
-        <v>227.8404998999999</v>
+        <v>226.20560175</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.261864450158884</v>
+        <v>0.2660275416841034</v>
       </c>
       <c r="T56">
-        <v>1.850761351118437</v>
+        <v>1.886421492758484</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.625885628138704</v>
+        <v>2.578142253081637</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1493711437578465</v>
+        <v>0.1491651404426064</v>
       </c>
       <c r="C57">
-        <v>1704.972763398682</v>
+        <v>1681.227892991042</v>
       </c>
       <c r="D57">
-        <v>3298.162763398682</v>
+        <v>3304.735892991042</v>
       </c>
       <c r="E57">
-        <v>1434.59</v>
+        <v>1464.908</v>
       </c>
       <c r="F57">
-        <v>1667.49</v>
+        <v>1697.808</v>
       </c>
       <c r="G57">
         <v>74.3</v>
@@ -5955,28 +5955,28 @@
         <v>309.1</v>
       </c>
       <c r="M57">
-        <v>119.892531</v>
+        <v>122.0723952</v>
       </c>
       <c r="N57">
-        <v>189.207469</v>
+        <v>187.0276048</v>
       </c>
       <c r="O57">
-        <v>47.30186725</v>
+        <v>46.7569012</v>
       </c>
       <c r="P57">
-        <v>141.90560175</v>
+        <v>140.2707036</v>
       </c>
       <c r="Q57">
-        <v>226.20560175</v>
+        <v>224.5707035999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2660275416841034</v>
+        <v>0.2703798646422872</v>
       </c>
       <c r="T57">
-        <v>1.886421492758484</v>
+        <v>1.923702549927624</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.578142253081637</v>
+        <v>2.532103998562322</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1491651404426064</v>
+        <v>0.1506263871273662</v>
       </c>
       <c r="C58">
-        <v>1681.227892991042</v>
+        <v>1604.842919779682</v>
       </c>
       <c r="D58">
-        <v>3304.735892991042</v>
+        <v>3258.668919779682</v>
       </c>
       <c r="E58">
-        <v>1464.908</v>
+        <v>1495.226</v>
       </c>
       <c r="F58">
-        <v>1697.808</v>
+        <v>1728.126</v>
       </c>
       <c r="G58">
         <v>74.3</v>
@@ -6037,45 +6037,45 @@
         <v>309.1</v>
       </c>
       <c r="M58">
-        <v>122.0723952</v>
+        <v>130.9919508</v>
       </c>
       <c r="N58">
-        <v>187.0276048</v>
+        <v>178.1080492</v>
       </c>
       <c r="O58">
-        <v>46.7569012</v>
+        <v>44.5270123</v>
       </c>
       <c r="P58">
-        <v>140.2707036</v>
+        <v>133.5810369</v>
       </c>
       <c r="Q58">
-        <v>224.5707035999999</v>
+        <v>217.8810369</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2703798646422872</v>
+        <v>0.2749346212264331</v>
       </c>
       <c r="T58">
-        <v>1.923702549927624</v>
+        <v>1.962717609755793</v>
       </c>
       <c r="U58">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.532103998562322</v>
+        <v>2.359686973987718</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1506263871273662</v>
+        <v>0.1504496338121261</v>
       </c>
       <c r="C59">
-        <v>1604.842919779682</v>
+        <v>1580.02881419249</v>
       </c>
       <c r="D59">
-        <v>3258.668919779682</v>
+        <v>3264.17281419249</v>
       </c>
       <c r="E59">
-        <v>1495.226</v>
+        <v>1525.544</v>
       </c>
       <c r="F59">
-        <v>1728.126</v>
+        <v>1758.444</v>
       </c>
       <c r="G59">
         <v>74.3</v>
@@ -6119,28 +6119,28 @@
         <v>309.1</v>
       </c>
       <c r="M59">
-        <v>130.9919508</v>
+        <v>133.2900552</v>
       </c>
       <c r="N59">
-        <v>178.1080492</v>
+        <v>175.8099448</v>
       </c>
       <c r="O59">
-        <v>44.5270123</v>
+        <v>43.9524862</v>
       </c>
       <c r="P59">
-        <v>133.5810369</v>
+        <v>131.8574586</v>
       </c>
       <c r="Q59">
-        <v>217.8810369</v>
+        <v>216.1574585999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2749346212264331</v>
+        <v>0.2797062709812527</v>
       </c>
       <c r="T59">
-        <v>1.962717609755793</v>
+        <v>2.003590529575781</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.359686973987718</v>
+        <v>2.319002715815515</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1504496338121261</v>
+        <v>0.150272880496886</v>
       </c>
       <c r="C60">
-        <v>1580.02881419249</v>
+        <v>1555.233332224741</v>
       </c>
       <c r="D60">
-        <v>3264.17281419249</v>
+        <v>3269.695332224741</v>
       </c>
       <c r="E60">
-        <v>1525.544</v>
+        <v>1555.862</v>
       </c>
       <c r="F60">
-        <v>1758.444</v>
+        <v>1788.762</v>
       </c>
       <c r="G60">
         <v>74.3</v>
@@ -6201,28 +6201,28 @@
         <v>309.1</v>
       </c>
       <c r="M60">
-        <v>133.2900552</v>
+        <v>135.5881596</v>
       </c>
       <c r="N60">
-        <v>175.8099448</v>
+        <v>173.5118404</v>
       </c>
       <c r="O60">
-        <v>43.9524862</v>
+        <v>43.3779601</v>
       </c>
       <c r="P60">
-        <v>131.8574586</v>
+        <v>130.1338803</v>
       </c>
       <c r="Q60">
-        <v>216.1574586</v>
+        <v>214.4338803</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2797062709812526</v>
+        <v>0.2847106841387463</v>
       </c>
       <c r="T60">
-        <v>2.003590529575781</v>
+        <v>2.046457250362597</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.319002715815516</v>
+        <v>2.279697585038981</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.150272880496886</v>
+        <v>0.1500961271816459</v>
       </c>
       <c r="C61">
-        <v>1555.233332224741</v>
+        <v>1530.456568562206</v>
       </c>
       <c r="D61">
-        <v>3269.695332224741</v>
+        <v>3275.236568562206</v>
       </c>
       <c r="E61">
-        <v>1555.862</v>
+        <v>1586.18</v>
       </c>
       <c r="F61">
-        <v>1788.762</v>
+        <v>1819.08</v>
       </c>
       <c r="G61">
         <v>74.3</v>
@@ -6283,28 +6283,28 @@
         <v>309.1</v>
       </c>
       <c r="M61">
-        <v>135.5881596</v>
+        <v>137.886264</v>
       </c>
       <c r="N61">
-        <v>173.5118404</v>
+        <v>171.213736</v>
       </c>
       <c r="O61">
-        <v>43.3779601</v>
+        <v>42.803434</v>
       </c>
       <c r="P61">
-        <v>130.1338803</v>
+        <v>128.410302</v>
       </c>
       <c r="Q61">
-        <v>214.4338803</v>
+        <v>212.710302</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2847106841387463</v>
+        <v>0.2899653179541146</v>
       </c>
       <c r="T61">
-        <v>2.046457250362597</v>
+        <v>2.091467307188754</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.279697585038981</v>
+        <v>2.241702625288332</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1500961271816459</v>
+        <v>0.1499193738664057</v>
       </c>
       <c r="C62">
-        <v>1530.456568562206</v>
+        <v>1505.698618533616</v>
       </c>
       <c r="D62">
-        <v>3275.236568562206</v>
+        <v>3280.796618533616</v>
       </c>
       <c r="E62">
-        <v>1586.18</v>
+        <v>1616.498</v>
       </c>
       <c r="F62">
-        <v>1819.08</v>
+        <v>1849.398</v>
       </c>
       <c r="G62">
         <v>74.3</v>
@@ -6365,28 +6365,28 @@
         <v>309.1</v>
       </c>
       <c r="M62">
-        <v>137.886264</v>
+        <v>140.1843684</v>
       </c>
       <c r="N62">
-        <v>171.213736</v>
+        <v>168.9156316</v>
       </c>
       <c r="O62">
-        <v>42.803434</v>
+        <v>42.2289079</v>
       </c>
       <c r="P62">
-        <v>128.410302</v>
+        <v>126.6867237</v>
       </c>
       <c r="Q62">
-        <v>212.710302</v>
+        <v>210.9867237</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2899653179541146</v>
+        <v>0.2954894201702711</v>
       </c>
       <c r="T62">
-        <v>2.091467307188754</v>
+        <v>2.138785572057277</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.241702625288332</v>
+        <v>2.204953401922949</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1499193738664057</v>
+        <v>0.1497426205511656</v>
       </c>
       <c r="C63">
-        <v>1505.698618533616</v>
+        <v>1480.959578116119</v>
       </c>
       <c r="D63">
-        <v>3280.796618533616</v>
+        <v>3286.375578116119</v>
       </c>
       <c r="E63">
-        <v>1616.498</v>
+        <v>1646.816</v>
       </c>
       <c r="F63">
-        <v>1849.398</v>
+        <v>1879.716</v>
       </c>
       <c r="G63">
         <v>74.3</v>
@@ -6447,28 +6447,28 @@
         <v>309.1</v>
       </c>
       <c r="M63">
-        <v>140.1843684</v>
+        <v>142.4824728</v>
       </c>
       <c r="N63">
-        <v>168.9156316</v>
+        <v>166.6175272</v>
       </c>
       <c r="O63">
-        <v>42.2289079</v>
+        <v>41.6543818</v>
       </c>
       <c r="P63">
-        <v>126.6867237</v>
+        <v>124.9631454</v>
       </c>
       <c r="Q63">
-        <v>210.9867237</v>
+        <v>209.2631454</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2954894201702711</v>
+        <v>0.3013042646083305</v>
       </c>
       <c r="T63">
-        <v>2.138785572057277</v>
+        <v>2.188594271918882</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.204953401922949</v>
+        <v>2.169389637375805</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1497426205511656</v>
+        <v>0.1495658672359255</v>
       </c>
       <c r="C64">
-        <v>1480.959578116119</v>
+        <v>1456.239543940811</v>
       </c>
       <c r="D64">
-        <v>3286.375578116119</v>
+        <v>3291.973543940811</v>
       </c>
       <c r="E64">
-        <v>1646.816</v>
+        <v>1677.134</v>
       </c>
       <c r="F64">
-        <v>1879.716</v>
+        <v>1910.034</v>
       </c>
       <c r="G64">
         <v>74.3</v>
@@ -6529,28 +6529,28 @@
         <v>309.1</v>
       </c>
       <c r="M64">
-        <v>142.4824728</v>
+        <v>144.7805772</v>
       </c>
       <c r="N64">
-        <v>166.6175272</v>
+        <v>164.3194228</v>
       </c>
       <c r="O64">
-        <v>41.6543818</v>
+        <v>41.0798557</v>
       </c>
       <c r="P64">
-        <v>124.9631454</v>
+        <v>123.2395671</v>
       </c>
       <c r="Q64">
-        <v>209.2631454</v>
+        <v>207.5395671</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3013042646083305</v>
+        <v>0.3074334249619607</v>
       </c>
       <c r="T64">
-        <v>2.188594271918882</v>
+        <v>2.241095333935167</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.169389637375805</v>
+        <v>2.134954881226983</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1495658672359255</v>
+        <v>0.1493891139206853</v>
       </c>
       <c r="C65">
-        <v>1456.239543940811</v>
+        <v>1431.53861329831</v>
       </c>
       <c r="D65">
-        <v>3291.973543940811</v>
+        <v>3297.59061329831</v>
       </c>
       <c r="E65">
-        <v>1677.134</v>
+        <v>1707.452</v>
       </c>
       <c r="F65">
-        <v>1910.034</v>
+        <v>1940.352</v>
       </c>
       <c r="G65">
         <v>74.3</v>
@@ -6611,28 +6611,28 @@
         <v>309.1</v>
       </c>
       <c r="M65">
-        <v>144.7805772</v>
+        <v>147.0786816</v>
       </c>
       <c r="N65">
-        <v>164.3194228</v>
+        <v>162.0213184</v>
       </c>
       <c r="O65">
-        <v>41.0798557</v>
+        <v>40.5053296</v>
       </c>
       <c r="P65">
-        <v>123.2395671</v>
+        <v>121.5159888</v>
       </c>
       <c r="Q65">
-        <v>207.5395671</v>
+        <v>205.8159888</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3074334249619607</v>
+        <v>0.3139030942241259</v>
       </c>
       <c r="T65">
-        <v>2.241095333935167</v>
+        <v>2.296513121619024</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.134954881226983</v>
+        <v>2.101596211207811</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1493891139206853</v>
+        <v>0.1492123606054452</v>
       </c>
       <c r="C66">
-        <v>1431.53861329831</v>
+        <v>1406.856884144394</v>
       </c>
       <c r="D66">
-        <v>3297.59061329831</v>
+        <v>3303.226884144394</v>
       </c>
       <c r="E66">
-        <v>1707.452</v>
+        <v>1737.77</v>
       </c>
       <c r="F66">
-        <v>1940.352</v>
+        <v>1970.67</v>
       </c>
       <c r="G66">
         <v>74.3</v>
@@ -6693,28 +6693,28 @@
         <v>309.1</v>
       </c>
       <c r="M66">
-        <v>147.0786816</v>
+        <v>149.376786</v>
       </c>
       <c r="N66">
-        <v>162.0213184</v>
+        <v>159.723214</v>
       </c>
       <c r="O66">
-        <v>40.5053296</v>
+        <v>39.9308035</v>
       </c>
       <c r="P66">
-        <v>121.5159888</v>
+        <v>119.7924105</v>
       </c>
       <c r="Q66">
-        <v>205.8159888</v>
+        <v>204.0924105</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3139030942241259</v>
+        <v>0.3207424588727005</v>
       </c>
       <c r="T66">
-        <v>2.296513121619024</v>
+        <v>2.355097640027672</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.101596211207811</v>
+        <v>2.069263961804614</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1492123606054452</v>
+        <v>0.149035607290205</v>
       </c>
       <c r="C67">
-        <v>1406.856884144394</v>
+        <v>1382.194455105697</v>
       </c>
       <c r="D67">
-        <v>3303.226884144394</v>
+        <v>3308.882455105697</v>
       </c>
       <c r="E67">
-        <v>1737.77</v>
+        <v>1768.088</v>
       </c>
       <c r="F67">
-        <v>1970.67</v>
+        <v>2000.988</v>
       </c>
       <c r="G67">
         <v>74.3</v>
@@ -6775,28 +6775,28 @@
         <v>309.1</v>
       </c>
       <c r="M67">
-        <v>149.376786</v>
+        <v>151.6748904</v>
       </c>
       <c r="N67">
-        <v>159.723214</v>
+        <v>157.4251096</v>
       </c>
       <c r="O67">
-        <v>39.9308035</v>
+        <v>39.3562774</v>
       </c>
       <c r="P67">
-        <v>119.7924105</v>
+        <v>118.0688322</v>
       </c>
       <c r="Q67">
-        <v>204.0924105</v>
+        <v>202.3688321999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3207424588727005</v>
+        <v>0.3279841390888384</v>
       </c>
       <c r="T67">
-        <v>2.355097640027672</v>
+        <v>2.417128306578006</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.069263961804614</v>
+        <v>2.037911477534847</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.149035607290205</v>
+        <v>0.1488588539749649</v>
       </c>
       <c r="C68">
-        <v>1382.194455105697</v>
+        <v>1357.551425485456</v>
       </c>
       <c r="D68">
-        <v>3308.882455105697</v>
+        <v>3314.557425485456</v>
       </c>
       <c r="E68">
-        <v>1768.088</v>
+        <v>1798.406</v>
       </c>
       <c r="F68">
-        <v>2000.988</v>
+        <v>2031.306</v>
       </c>
       <c r="G68">
         <v>74.3</v>
@@ -6857,28 +6857,28 @@
         <v>309.1</v>
       </c>
       <c r="M68">
-        <v>151.6748904</v>
+        <v>153.9729948</v>
       </c>
       <c r="N68">
-        <v>157.4251096</v>
+        <v>155.1270052</v>
       </c>
       <c r="O68">
-        <v>39.3562774</v>
+        <v>38.7817513</v>
       </c>
       <c r="P68">
-        <v>118.0688322</v>
+        <v>116.3452539</v>
       </c>
       <c r="Q68">
-        <v>202.3688321999999</v>
+        <v>200.6452538999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3279841390888384</v>
+        <v>0.3356647090150451</v>
       </c>
       <c r="T68">
-        <v>2.417128306578006</v>
+        <v>2.482918407464723</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.037911477534847</v>
+        <v>2.007494888317908</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1488588539749649</v>
+        <v>0.1559241006597248</v>
       </c>
       <c r="C69">
-        <v>1357.551425485456</v>
+        <v>1114.580920524552</v>
       </c>
       <c r="D69">
-        <v>3314.557425485456</v>
+        <v>3101.904920524552</v>
       </c>
       <c r="E69">
-        <v>1798.406</v>
+        <v>1828.724</v>
       </c>
       <c r="F69">
-        <v>2031.306</v>
+        <v>2061.624</v>
       </c>
       <c r="G69">
         <v>74.3</v>
@@ -6939,45 +6939,45 @@
         <v>309.1</v>
       </c>
       <c r="M69">
-        <v>153.9729948</v>
+        <v>185.54616</v>
       </c>
       <c r="N69">
-        <v>155.1270052</v>
+        <v>123.55384</v>
       </c>
       <c r="O69">
-        <v>38.7817513</v>
+        <v>30.88846</v>
       </c>
       <c r="P69">
-        <v>116.3452539</v>
+        <v>92.66538</v>
       </c>
       <c r="Q69">
-        <v>200.6452538999999</v>
+        <v>176.96538</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3356647090150451</v>
+        <v>0.3438253145616399</v>
       </c>
       <c r="T69">
-        <v>2.482918407464723</v>
+        <v>2.552820389656862</v>
       </c>
       <c r="U69">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.007494888317908</v>
+        <v>1.66589273526329</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1559241006597248</v>
+        <v>0.1558538473444847</v>
       </c>
       <c r="C70">
-        <v>1114.580920524552</v>
+        <v>1086.243033982505</v>
       </c>
       <c r="D70">
-        <v>3101.904920524552</v>
+        <v>3103.885033982506</v>
       </c>
       <c r="E70">
-        <v>1828.724</v>
+        <v>1859.042</v>
       </c>
       <c r="F70">
-        <v>2061.624</v>
+        <v>2091.942</v>
       </c>
       <c r="G70">
         <v>74.3</v>
@@ -7021,28 +7021,28 @@
         <v>309.1</v>
       </c>
       <c r="M70">
-        <v>185.54616</v>
+        <v>188.27478</v>
       </c>
       <c r="N70">
-        <v>123.55384</v>
+        <v>120.82522</v>
       </c>
       <c r="O70">
-        <v>30.88846</v>
+        <v>30.206305</v>
       </c>
       <c r="P70">
-        <v>92.66538</v>
+        <v>90.618915</v>
       </c>
       <c r="Q70">
-        <v>176.96538</v>
+        <v>174.918915</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3438253145616399</v>
+        <v>0.3525124107886602</v>
       </c>
       <c r="T70">
-        <v>2.552820389656862</v>
+        <v>2.627232177151718</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.66589273526329</v>
+        <v>1.641749362288459</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1558538473444847</v>
+        <v>0.1557835940292445</v>
       </c>
       <c r="C71">
-        <v>1086.243033982505</v>
+        <v>1057.907677082017</v>
       </c>
       <c r="D71">
-        <v>3103.885033982506</v>
+        <v>3105.867677082018</v>
       </c>
       <c r="E71">
-        <v>1859.042</v>
+        <v>1889.36</v>
       </c>
       <c r="F71">
-        <v>2091.942</v>
+        <v>2122.26</v>
       </c>
       <c r="G71">
         <v>74.3</v>
@@ -7103,28 +7103,28 @@
         <v>309.1</v>
       </c>
       <c r="M71">
-        <v>188.27478</v>
+        <v>191.0034</v>
       </c>
       <c r="N71">
-        <v>120.82522</v>
+        <v>118.0966</v>
       </c>
       <c r="O71">
-        <v>30.206305</v>
+        <v>29.52415000000001</v>
       </c>
       <c r="P71">
-        <v>90.618915</v>
+        <v>88.57245000000002</v>
       </c>
       <c r="Q71">
-        <v>174.918915</v>
+        <v>172.87245</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3525124107886602</v>
+        <v>0.3617786467641484</v>
       </c>
       <c r="T71">
-        <v>2.627232177151718</v>
+        <v>2.706604750479564</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.641749362288459</v>
+        <v>1.618295799970053</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1557835940292445</v>
+        <v>0.1557133407140044</v>
       </c>
       <c r="C72">
-        <v>1057.907677082017</v>
+        <v>1029.574854673697</v>
       </c>
       <c r="D72">
-        <v>3105.867677082018</v>
+        <v>3107.852854673697</v>
       </c>
       <c r="E72">
-        <v>1889.36</v>
+        <v>1919.678</v>
       </c>
       <c r="F72">
-        <v>2122.26</v>
+        <v>2152.578</v>
       </c>
       <c r="G72">
         <v>74.3</v>
@@ -7185,28 +7185,28 @@
         <v>309.1</v>
       </c>
       <c r="M72">
-        <v>191.0034</v>
+        <v>193.73202</v>
       </c>
       <c r="N72">
-        <v>118.0966</v>
+        <v>115.36798</v>
       </c>
       <c r="O72">
-        <v>29.52415000000001</v>
+        <v>28.841995</v>
       </c>
       <c r="P72">
-        <v>88.57245000000002</v>
+        <v>86.52598499999999</v>
       </c>
       <c r="Q72">
-        <v>172.87245</v>
+        <v>170.8259849999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3617786467641484</v>
+        <v>0.3716839334965669</v>
       </c>
       <c r="T72">
-        <v>2.706604750479564</v>
+        <v>2.791451294381745</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.618295799970053</v>
+        <v>1.595502901378925</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1557133407140044</v>
+        <v>0.1556430873987643</v>
       </c>
       <c r="C73">
-        <v>1029.574854673698</v>
+        <v>1001.244571620569</v>
       </c>
       <c r="D73">
-        <v>3107.852854673697</v>
+        <v>3109.840571620569</v>
       </c>
       <c r="E73">
-        <v>1919.678</v>
+        <v>1949.996</v>
       </c>
       <c r="F73">
-        <v>2152.578</v>
+        <v>2182.896</v>
       </c>
       <c r="G73">
         <v>74.3</v>
@@ -7267,28 +7267,28 @@
         <v>309.1</v>
       </c>
       <c r="M73">
-        <v>193.73202</v>
+        <v>196.46064</v>
       </c>
       <c r="N73">
-        <v>115.36798</v>
+        <v>112.63936</v>
       </c>
       <c r="O73">
-        <v>28.84199500000001</v>
+        <v>28.15984</v>
       </c>
       <c r="P73">
-        <v>86.52598500000003</v>
+        <v>84.47952000000001</v>
       </c>
       <c r="Q73">
-        <v>170.825985</v>
+        <v>168.77952</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3716839334965668</v>
+        <v>0.3822967407098722</v>
       </c>
       <c r="T73">
-        <v>2.791451294381744</v>
+        <v>2.882358305705509</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.595502901378926</v>
+        <v>1.573343138859774</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1556430873987643</v>
+        <v>0.1555728340835241</v>
       </c>
       <c r="C74">
-        <v>1001.244571620569</v>
+        <v>972.916832798107</v>
       </c>
       <c r="D74">
-        <v>3109.840571620569</v>
+        <v>3111.830832798107</v>
       </c>
       <c r="E74">
-        <v>1949.996</v>
+        <v>1980.314</v>
       </c>
       <c r="F74">
-        <v>2182.896</v>
+        <v>2213.214</v>
       </c>
       <c r="G74">
         <v>74.3</v>
@@ -7349,28 +7349,28 @@
         <v>309.1</v>
       </c>
       <c r="M74">
-        <v>196.46064</v>
+        <v>199.18926</v>
       </c>
       <c r="N74">
-        <v>112.63936</v>
+        <v>109.91074</v>
       </c>
       <c r="O74">
-        <v>28.15984</v>
+        <v>27.47768500000001</v>
       </c>
       <c r="P74">
-        <v>84.47952000000001</v>
+        <v>82.43305500000002</v>
       </c>
       <c r="Q74">
-        <v>168.77952</v>
+        <v>166.733055</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3822967407098722</v>
+        <v>0.39369568179083</v>
       </c>
       <c r="T74">
-        <v>2.882358305705509</v>
+        <v>2.979999169719923</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.573343138859774</v>
+        <v>1.551790493121969</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1555728340835241</v>
+        <v>0.155502580768284</v>
       </c>
       <c r="C75">
-        <v>972.916832798107</v>
+        <v>944.5916430942689</v>
       </c>
       <c r="D75">
-        <v>3111.830832798107</v>
+        <v>3113.823643094269</v>
       </c>
       <c r="E75">
-        <v>1980.314</v>
+        <v>2010.632</v>
       </c>
       <c r="F75">
-        <v>2213.214</v>
+        <v>2243.532</v>
       </c>
       <c r="G75">
         <v>74.3</v>
@@ -7431,28 +7431,28 @@
         <v>309.1</v>
       </c>
       <c r="M75">
-        <v>199.18926</v>
+        <v>201.91788</v>
       </c>
       <c r="N75">
-        <v>109.91074</v>
+        <v>107.18212</v>
       </c>
       <c r="O75">
-        <v>27.47768500000001</v>
+        <v>26.79553000000001</v>
       </c>
       <c r="P75">
-        <v>82.43305500000002</v>
+        <v>80.38659000000001</v>
       </c>
       <c r="Q75">
-        <v>166.733055</v>
+        <v>164.68659</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.39369568179083</v>
+        <v>0.4059714644933998</v>
       </c>
       <c r="T75">
-        <v>2.979999169719923</v>
+        <v>3.085150869427754</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.551790493121969</v>
+        <v>1.530820351323023</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.155502580768284</v>
+        <v>0.1554323274530438</v>
       </c>
       <c r="C76">
-        <v>944.5916430942689</v>
+        <v>916.2690074095453</v>
       </c>
       <c r="D76">
-        <v>3113.823643094269</v>
+        <v>3115.819007409546</v>
       </c>
       <c r="E76">
-        <v>2010.632</v>
+        <v>2040.95</v>
       </c>
       <c r="F76">
-        <v>2243.532</v>
+        <v>2273.85</v>
       </c>
       <c r="G76">
         <v>74.3</v>
@@ -7513,28 +7513,28 @@
         <v>309.1</v>
       </c>
       <c r="M76">
-        <v>201.91788</v>
+        <v>204.6465</v>
       </c>
       <c r="N76">
-        <v>107.18212</v>
+        <v>104.4535</v>
       </c>
       <c r="O76">
-        <v>26.79553000000001</v>
+        <v>26.113375</v>
       </c>
       <c r="P76">
-        <v>80.38659000000001</v>
+        <v>78.340125</v>
       </c>
       <c r="Q76">
-        <v>164.68659</v>
+        <v>162.640125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4059714644933998</v>
+        <v>0.4192293098121753</v>
       </c>
       <c r="T76">
-        <v>3.085150869427754</v>
+        <v>3.198714705112211</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.530820351323023</v>
+        <v>1.510409413305382</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1554323274530438</v>
+        <v>0.1920234175765142</v>
       </c>
       <c r="C77">
-        <v>916.2690074095453</v>
+        <v>106.2454308462966</v>
       </c>
       <c r="D77">
-        <v>3115.819007409546</v>
+        <v>2336.113430846297</v>
       </c>
       <c r="E77">
-        <v>2040.95</v>
+        <v>2071.268</v>
       </c>
       <c r="F77">
-        <v>2273.85</v>
+        <v>2304.168</v>
       </c>
       <c r="G77">
         <v>74.3</v>
@@ -7595,45 +7595,45 @@
         <v>309.1</v>
       </c>
       <c r="M77">
-        <v>204.6465</v>
+        <v>338.2518624000001</v>
       </c>
       <c r="N77">
-        <v>104.4535</v>
+        <v>-29.15186240000003</v>
       </c>
       <c r="O77">
-        <v>26.113375</v>
+        <v>-7.287965600000007</v>
       </c>
       <c r="P77">
-        <v>78.340125</v>
+        <v>-21.86389680000002</v>
       </c>
       <c r="Q77">
-        <v>162.640125</v>
+        <v>62.43610319999993</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4192293098121753</v>
+        <v>0.4414315684418438</v>
       </c>
       <c r="T77">
-        <v>3.198714705112211</v>
+        <v>3.3888944507812</v>
       </c>
       <c r="U77">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.25</v>
+        <v>0.2284540266880139</v>
       </c>
       <c r="W77">
-        <v>0.0675</v>
+        <v>0.1132629488821996</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.510409413305382</v>
+        <v>0.9138161067520555</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1920234175765142</v>
+        <v>0.1930334175765142</v>
       </c>
       <c r="C78">
-        <v>106.2454308462966</v>
+        <v>59.90202979270362</v>
       </c>
       <c r="D78">
-        <v>2336.113430846297</v>
+        <v>2320.088029792704</v>
       </c>
       <c r="E78">
-        <v>2071.268</v>
+        <v>2101.586</v>
       </c>
       <c r="F78">
-        <v>2304.168</v>
+        <v>2334.486</v>
       </c>
       <c r="G78">
         <v>74.3</v>
@@ -7677,37 +7677,37 @@
         <v>309.1</v>
       </c>
       <c r="M78">
-        <v>338.2518624000001</v>
+        <v>342.7025448000001</v>
       </c>
       <c r="N78">
-        <v>-29.15186240000003</v>
+        <v>-33.60254480000003</v>
       </c>
       <c r="O78">
-        <v>-7.287965600000007</v>
+        <v>-8.400636200000008</v>
       </c>
       <c r="P78">
-        <v>-21.86389680000002</v>
+        <v>-25.20190860000002</v>
       </c>
       <c r="Q78">
-        <v>62.43610319999993</v>
+        <v>59.09809139999993</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4414315684418438</v>
+        <v>0.4586329409827936</v>
       </c>
       <c r="T78">
-        <v>3.3888944507812</v>
+        <v>3.536237687771686</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2284540266880139</v>
+        <v>0.2254870912764812</v>
       </c>
       <c r="W78">
-        <v>0.1132629488821996</v>
+        <v>0.1136984950006126</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9138161067520555</v>
+        <v>0.9019483651059249</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1930334175765142</v>
+        <v>0.1940434175765142</v>
       </c>
       <c r="C79">
-        <v>59.90202979270362</v>
+        <v>13.77699465820206</v>
       </c>
       <c r="D79">
-        <v>2320.088029792704</v>
+        <v>2304.280994658202</v>
       </c>
       <c r="E79">
-        <v>2101.586</v>
+        <v>2131.904</v>
       </c>
       <c r="F79">
-        <v>2334.486</v>
+        <v>2364.804</v>
       </c>
       <c r="G79">
         <v>74.3</v>
@@ -7759,37 +7759,37 @@
         <v>309.1</v>
       </c>
       <c r="M79">
-        <v>342.7025448000001</v>
+        <v>347.1532272000001</v>
       </c>
       <c r="N79">
-        <v>-33.60254480000003</v>
+        <v>-38.05322720000004</v>
       </c>
       <c r="O79">
-        <v>-8.400636200000008</v>
+        <v>-9.513306800000009</v>
       </c>
       <c r="P79">
-        <v>-25.20190860000002</v>
+        <v>-28.53992040000003</v>
       </c>
       <c r="Q79">
-        <v>59.09809139999993</v>
+        <v>55.76007959999993</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4586329409827936</v>
+        <v>0.4773980746638296</v>
       </c>
       <c r="T79">
-        <v>3.536237687771686</v>
+        <v>3.696975764488581</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2254870912764812</v>
+        <v>0.2225962311319109</v>
       </c>
       <c r="W79">
-        <v>0.1136984950006126</v>
+        <v>0.1141228732698355</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9019483651059249</v>
+        <v>0.8903849245276437</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1940434175765142</v>
+        <v>0.1950534175765142</v>
       </c>
       <c r="C80">
-        <v>13.77699465820206</v>
+        <v>-32.13410761305295</v>
       </c>
       <c r="D80">
-        <v>2304.280994658202</v>
+        <v>2288.687892386947</v>
       </c>
       <c r="E80">
-        <v>2131.904</v>
+        <v>2162.222</v>
       </c>
       <c r="F80">
-        <v>2364.804</v>
+        <v>2395.122</v>
       </c>
       <c r="G80">
         <v>74.3</v>
@@ -7841,37 +7841,37 @@
         <v>309.1</v>
       </c>
       <c r="M80">
-        <v>347.1532272000001</v>
+        <v>351.6039096000001</v>
       </c>
       <c r="N80">
-        <v>-38.05322720000004</v>
+        <v>-42.50390960000004</v>
       </c>
       <c r="O80">
-        <v>-9.513306800000009</v>
+        <v>-10.62597740000001</v>
       </c>
       <c r="P80">
-        <v>-28.53992040000003</v>
+        <v>-31.87793220000003</v>
       </c>
       <c r="Q80">
-        <v>55.76007959999993</v>
+        <v>52.42206779999992</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4773980746638296</v>
+        <v>0.4979503639335359</v>
       </c>
       <c r="T80">
-        <v>3.696975764488581</v>
+        <v>3.873022229464228</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2225962311319109</v>
+        <v>0.2197785573201146</v>
       </c>
       <c r="W80">
-        <v>0.1141228732698355</v>
+        <v>0.1145365077854072</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8903849245276437</v>
+        <v>0.8791142292804583</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1950534175765142</v>
+        <v>0.1960634175765142</v>
       </c>
       <c r="C81">
-        <v>-32.13410761305295</v>
+        <v>-77.83559088923812</v>
       </c>
       <c r="D81">
-        <v>2288.687892386947</v>
+        <v>2273.304409110762</v>
       </c>
       <c r="E81">
-        <v>2162.222</v>
+        <v>2192.54</v>
       </c>
       <c r="F81">
-        <v>2395.122</v>
+        <v>2425.44</v>
       </c>
       <c r="G81">
         <v>74.3</v>
@@ -7923,37 +7923,37 @@
         <v>309.1</v>
       </c>
       <c r="M81">
-        <v>351.6039096000001</v>
+        <v>356.054592</v>
       </c>
       <c r="N81">
-        <v>-42.50390960000004</v>
+        <v>-46.95459199999999</v>
       </c>
       <c r="O81">
-        <v>-10.62597740000001</v>
+        <v>-11.738648</v>
       </c>
       <c r="P81">
-        <v>-31.87793220000003</v>
+        <v>-35.21594399999999</v>
       </c>
       <c r="Q81">
-        <v>52.42206779999992</v>
+        <v>49.08405599999996</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4979503639335359</v>
+        <v>0.5205578821302126</v>
       </c>
       <c r="T81">
-        <v>3.873022229464228</v>
+        <v>4.06667334093744</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2197785573201146</v>
+        <v>0.2170313253536132</v>
       </c>
       <c r="W81">
-        <v>0.1145365077854072</v>
+        <v>0.1149398014380896</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8791142292804583</v>
+        <v>0.8681253014144528</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1960634175765142</v>
+        <v>0.1970734175765142</v>
       </c>
       <c r="C82">
-        <v>-77.83559088923812</v>
+        <v>-123.3316538297454</v>
       </c>
       <c r="D82">
-        <v>2273.304409110762</v>
+        <v>2258.126346170255</v>
       </c>
       <c r="E82">
-        <v>2192.54</v>
+        <v>2222.858</v>
       </c>
       <c r="F82">
-        <v>2425.44</v>
+        <v>2455.758</v>
       </c>
       <c r="G82">
         <v>74.3</v>
@@ -8005,37 +8005,37 @@
         <v>309.1</v>
       </c>
       <c r="M82">
-        <v>356.054592</v>
+        <v>360.5052744000001</v>
       </c>
       <c r="N82">
-        <v>-46.95459199999999</v>
+        <v>-51.40527440000005</v>
       </c>
       <c r="O82">
-        <v>-11.738648</v>
+        <v>-12.85131860000001</v>
       </c>
       <c r="P82">
-        <v>-35.21594399999999</v>
+        <v>-38.55395580000004</v>
       </c>
       <c r="Q82">
-        <v>49.08405599999996</v>
+        <v>45.74604419999991</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5205578821302126</v>
+        <v>0.5455451390844344</v>
       </c>
       <c r="T82">
-        <v>4.06667334093744</v>
+        <v>4.280708779934147</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2170313253536132</v>
+        <v>0.2143519262751735</v>
       </c>
       <c r="W82">
-        <v>0.1149398014380896</v>
+        <v>0.1153331372228045</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8681253014144528</v>
+        <v>0.857407705100694</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1970734175765142</v>
+        <v>0.1980834175765142</v>
       </c>
       <c r="C83">
-        <v>-123.3316538297454</v>
+        <v>-168.6263837057081</v>
       </c>
       <c r="D83">
-        <v>2258.126346170255</v>
+        <v>2243.149616294292</v>
       </c>
       <c r="E83">
-        <v>2222.858</v>
+        <v>2253.176</v>
       </c>
       <c r="F83">
-        <v>2455.758</v>
+        <v>2486.076</v>
       </c>
       <c r="G83">
         <v>74.3</v>
@@ -8087,37 +8087,37 @@
         <v>309.1</v>
       </c>
       <c r="M83">
-        <v>360.5052744000001</v>
+        <v>364.9559568000001</v>
       </c>
       <c r="N83">
-        <v>-51.40527440000005</v>
+        <v>-55.85595680000006</v>
       </c>
       <c r="O83">
-        <v>-12.85131860000001</v>
+        <v>-13.96398920000001</v>
       </c>
       <c r="P83">
-        <v>-38.55395580000004</v>
+        <v>-41.89196760000004</v>
       </c>
       <c r="Q83">
-        <v>45.74604419999991</v>
+        <v>42.40803239999991</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5455451390844344</v>
+        <v>0.5733087579224585</v>
       </c>
       <c r="T83">
-        <v>4.280708779934147</v>
+        <v>4.518525934374933</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2143519262751735</v>
+        <v>0.2117378783937689</v>
       </c>
       <c r="W83">
-        <v>0.1153331372228045</v>
+        <v>0.1157168794517947</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.857407705100694</v>
+        <v>0.8469515135750757</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1980834175765142</v>
+        <v>0.1990934175765142</v>
       </c>
       <c r="C84">
-        <v>-168.6263837057081</v>
+        <v>-213.7237600695134</v>
       </c>
       <c r="D84">
-        <v>2243.149616294292</v>
+        <v>2228.370239930487</v>
       </c>
       <c r="E84">
-        <v>2253.176</v>
+        <v>2283.494</v>
       </c>
       <c r="F84">
-        <v>2486.076</v>
+        <v>2516.394</v>
       </c>
       <c r="G84">
         <v>74.3</v>
@@ -8169,37 +8169,37 @@
         <v>309.1</v>
       </c>
       <c r="M84">
-        <v>364.9559568000001</v>
+        <v>369.4066392000001</v>
       </c>
       <c r="N84">
-        <v>-55.85595680000006</v>
+        <v>-60.30663920000006</v>
       </c>
       <c r="O84">
-        <v>-13.96398920000001</v>
+        <v>-15.07665980000002</v>
       </c>
       <c r="P84">
-        <v>-41.89196760000004</v>
+        <v>-45.22997940000005</v>
       </c>
       <c r="Q84">
-        <v>42.40803239999991</v>
+        <v>39.07002059999991</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5733087579224585</v>
+        <v>0.6043386848590738</v>
       </c>
       <c r="T84">
-        <v>4.518525934374933</v>
+        <v>4.78432157757346</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2117378783937689</v>
+        <v>0.2091868196179404</v>
       </c>
       <c r="W84">
-        <v>0.1157168794517947</v>
+        <v>0.1160913748800864</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8469515135750757</v>
+        <v>0.8367472784717616</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1990934175765142</v>
+        <v>0.2001034175765142</v>
       </c>
       <c r="C85">
-        <v>-213.7237600695134</v>
+        <v>-258.6276582801847</v>
       </c>
       <c r="D85">
-        <v>2228.370239930487</v>
+        <v>2213.784341719816</v>
       </c>
       <c r="E85">
-        <v>2283.494</v>
+        <v>2313.812</v>
       </c>
       <c r="F85">
-        <v>2516.394</v>
+        <v>2546.712</v>
       </c>
       <c r="G85">
         <v>74.3</v>
@@ -8251,37 +8251,37 @@
         <v>309.1</v>
       </c>
       <c r="M85">
-        <v>369.4066392000001</v>
+        <v>373.8573216000001</v>
       </c>
       <c r="N85">
-        <v>-60.30663920000006</v>
+        <v>-64.75732160000007</v>
       </c>
       <c r="O85">
-        <v>-15.07665980000002</v>
+        <v>-16.18933040000002</v>
       </c>
       <c r="P85">
-        <v>-45.22997940000005</v>
+        <v>-48.56799120000005</v>
       </c>
       <c r="Q85">
-        <v>39.07002059999991</v>
+        <v>35.7320087999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6043386848590738</v>
+        <v>0.6392473526627659</v>
       </c>
       <c r="T85">
-        <v>4.78432157757346</v>
+        <v>5.083341676171801</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2091868196179404</v>
+        <v>0.2066965003367744</v>
       </c>
       <c r="W85">
-        <v>0.1160913748800864</v>
+        <v>0.1164569537505615</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8367472784717616</v>
+        <v>0.8267860013470978</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2001034175765142</v>
+        <v>0.2011134175765142</v>
       </c>
       <c r="C86">
-        <v>-258.6276582801843</v>
+        <v>-303.341852891223</v>
       </c>
       <c r="D86">
-        <v>2213.784341719816</v>
+        <v>2199.388147108777</v>
       </c>
       <c r="E86">
-        <v>2313.812</v>
+        <v>2344.13</v>
       </c>
       <c r="F86">
-        <v>2546.712</v>
+        <v>2577.03</v>
       </c>
       <c r="G86">
         <v>74.3</v>
@@ -8333,37 +8333,37 @@
         <v>309.1</v>
       </c>
       <c r="M86">
-        <v>373.8573216</v>
+        <v>378.308004</v>
       </c>
       <c r="N86">
-        <v>-64.75732160000001</v>
+        <v>-69.20800400000002</v>
       </c>
       <c r="O86">
-        <v>-16.1893304</v>
+        <v>-17.302001</v>
       </c>
       <c r="P86">
-        <v>-48.56799120000001</v>
+        <v>-51.90600300000001</v>
       </c>
       <c r="Q86">
-        <v>35.73200879999995</v>
+        <v>32.39399699999994</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6392473526627656</v>
+        <v>0.6788105095069499</v>
       </c>
       <c r="T86">
-        <v>5.083341676171798</v>
+        <v>5.422231121249918</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2066965003367745</v>
+        <v>0.2042647768034006</v>
       </c>
       <c r="W86">
-        <v>0.1164569537505615</v>
+        <v>0.1168139307652608</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8267860013470978</v>
+        <v>0.8170591072136025</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2011134175765142</v>
+        <v>0.2021234175765141</v>
       </c>
       <c r="C87">
-        <v>-303.341852891223</v>
+        <v>-347.8700209071094</v>
       </c>
       <c r="D87">
-        <v>2199.388147108777</v>
+        <v>2185.17797909289</v>
       </c>
       <c r="E87">
-        <v>2344.13</v>
+        <v>2374.448</v>
       </c>
       <c r="F87">
-        <v>2577.03</v>
+        <v>2607.348</v>
       </c>
       <c r="G87">
         <v>74.3</v>
@@ -8415,37 +8415,37 @@
         <v>309.1</v>
       </c>
       <c r="M87">
-        <v>378.308004</v>
+        <v>382.7586864</v>
       </c>
       <c r="N87">
-        <v>-69.20800400000002</v>
+        <v>-73.65868640000002</v>
       </c>
       <c r="O87">
-        <v>-17.302001</v>
+        <v>-18.41467160000001</v>
       </c>
       <c r="P87">
-        <v>-51.90600300000001</v>
+        <v>-55.24401480000002</v>
       </c>
       <c r="Q87">
-        <v>32.39399699999994</v>
+        <v>29.05598519999994</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6788105095069499</v>
+        <v>0.7240255459003034</v>
       </c>
       <c r="T87">
-        <v>5.422231121249918</v>
+        <v>5.80953334419634</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2042647768034006</v>
+        <v>0.2018896049801053</v>
       </c>
       <c r="W87">
-        <v>0.1168139307652608</v>
+        <v>0.1171626059889205</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8170591072136025</v>
+        <v>0.8075584199204211</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2021234175765141</v>
+        <v>0.255478390097334</v>
       </c>
       <c r="C88">
-        <v>-347.8700209071094</v>
+        <v>-934.2305915004836</v>
       </c>
       <c r="D88">
-        <v>2185.17797909289</v>
+        <v>1629.135408499517</v>
       </c>
       <c r="E88">
-        <v>2374.448</v>
+        <v>2404.766</v>
       </c>
       <c r="F88">
-        <v>2607.348</v>
+        <v>2637.666</v>
       </c>
       <c r="G88">
         <v>74.3</v>
@@ -8497,45 +8497,45 @@
         <v>309.1</v>
       </c>
       <c r="M88">
-        <v>382.7586864</v>
+        <v>529.6433328000001</v>
       </c>
       <c r="N88">
-        <v>-73.65868640000002</v>
+        <v>-220.5433328</v>
       </c>
       <c r="O88">
-        <v>-18.41467160000001</v>
+        <v>-55.13583320000001</v>
       </c>
       <c r="P88">
-        <v>-55.24401480000002</v>
+        <v>-165.4074996</v>
       </c>
       <c r="Q88">
-        <v>29.05598519999994</v>
+        <v>-81.10749960000007</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7240255459003034</v>
+        <v>0.81746576112971</v>
       </c>
       <c r="T88">
-        <v>5.80953334419634</v>
+        <v>6.609922019240314</v>
       </c>
       <c r="U88">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.2018896049801053</v>
+        <v>0.1459000712639576</v>
       </c>
       <c r="W88">
-        <v>0.1171626059889205</v>
+        <v>0.1715032656901973</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.8075584199204211</v>
+        <v>0.5836002850558303</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.255478390097334</v>
+        <v>0.257028390097334</v>
       </c>
       <c r="C89">
-        <v>-934.2305915004836</v>
+        <v>-976.5032339707063</v>
       </c>
       <c r="D89">
-        <v>1629.135408499517</v>
+        <v>1617.180766029294</v>
       </c>
       <c r="E89">
-        <v>2404.766</v>
+        <v>2435.084</v>
       </c>
       <c r="F89">
-        <v>2637.666</v>
+        <v>2667.984</v>
       </c>
       <c r="G89">
         <v>74.3</v>
@@ -8579,37 +8579,37 @@
         <v>309.1</v>
       </c>
       <c r="M89">
-        <v>529.6433328000001</v>
+        <v>535.7311872000001</v>
       </c>
       <c r="N89">
-        <v>-220.5433328</v>
+        <v>-226.6311872000001</v>
       </c>
       <c r="O89">
-        <v>-55.13583320000001</v>
+        <v>-56.65779680000003</v>
       </c>
       <c r="P89">
-        <v>-165.4074996</v>
+        <v>-169.9733904000001</v>
       </c>
       <c r="Q89">
-        <v>-81.10749960000007</v>
+        <v>-85.67339040000013</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.81746576112971</v>
+        <v>0.8817712412238526</v>
       </c>
       <c r="T89">
-        <v>6.609922019240314</v>
+        <v>7.160748854177008</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1459000712639576</v>
+        <v>0.1442421159086853</v>
       </c>
       <c r="W89">
-        <v>0.1715032656901973</v>
+        <v>0.171836183125536</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5836002850558303</v>
+        <v>0.5769684636347412</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.257028390097334</v>
+        <v>0.258578390097334</v>
       </c>
       <c r="C90">
-        <v>-976.5032339707063</v>
+        <v>-1018.601707477432</v>
       </c>
       <c r="D90">
-        <v>1617.180766029294</v>
+        <v>1605.400292522569</v>
       </c>
       <c r="E90">
-        <v>2435.084</v>
+        <v>2465.402</v>
       </c>
       <c r="F90">
-        <v>2667.984</v>
+        <v>2698.302</v>
       </c>
       <c r="G90">
         <v>74.3</v>
@@ -8661,37 +8661,37 @@
         <v>309.1</v>
       </c>
       <c r="M90">
-        <v>535.7311872000001</v>
+        <v>541.8190416</v>
       </c>
       <c r="N90">
-        <v>-226.6311872000001</v>
+        <v>-232.7190416</v>
       </c>
       <c r="O90">
-        <v>-56.65779680000003</v>
+        <v>-58.17976039999999</v>
       </c>
       <c r="P90">
-        <v>-169.9733904000001</v>
+        <v>-174.5392812</v>
       </c>
       <c r="Q90">
-        <v>-85.67339040000013</v>
+        <v>-90.23928120000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8817712412238526</v>
+        <v>0.9577686267896575</v>
       </c>
       <c r="T90">
-        <v>7.160748854177008</v>
+        <v>7.811726022738554</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1442421159086853</v>
+        <v>0.1426214179771271</v>
       </c>
       <c r="W90">
-        <v>0.171836183125536</v>
+        <v>0.1721616192701929</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5769684636347412</v>
+        <v>0.5704856719085083</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.258578390097334</v>
+        <v>0.260128390097334</v>
       </c>
       <c r="C91">
-        <v>-1018.601707477432</v>
+        <v>-1060.529790734624</v>
       </c>
       <c r="D91">
-        <v>1605.400292522569</v>
+        <v>1593.790209265376</v>
       </c>
       <c r="E91">
-        <v>2465.402</v>
+        <v>2495.72</v>
       </c>
       <c r="F91">
-        <v>2698.302</v>
+        <v>2728.62</v>
       </c>
       <c r="G91">
         <v>74.3</v>
@@ -8743,37 +8743,37 @@
         <v>309.1</v>
       </c>
       <c r="M91">
-        <v>541.8190416</v>
+        <v>547.9068960000001</v>
       </c>
       <c r="N91">
-        <v>-232.7190416</v>
+        <v>-238.8068960000001</v>
       </c>
       <c r="O91">
-        <v>-58.17976039999999</v>
+        <v>-59.70172400000001</v>
       </c>
       <c r="P91">
-        <v>-174.5392812</v>
+        <v>-179.105172</v>
       </c>
       <c r="Q91">
-        <v>-90.23928120000002</v>
+        <v>-94.80517200000008</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9577686267896575</v>
+        <v>1.048965489468623</v>
       </c>
       <c r="T91">
-        <v>7.811726022738554</v>
+        <v>8.59289862501241</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1426214179771271</v>
+        <v>0.141036735555159</v>
       </c>
       <c r="W91">
-        <v>0.1721616192701929</v>
+        <v>0.1724798235005241</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5704856719085083</v>
+        <v>0.564146942220636</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.260128390097334</v>
+        <v>0.261678390097334</v>
       </c>
       <c r="C92">
-        <v>-1060.529790734624</v>
+        <v>-1102.291153932058</v>
       </c>
       <c r="D92">
-        <v>1593.790209265376</v>
+        <v>1582.346846067942</v>
       </c>
       <c r="E92">
-        <v>2495.72</v>
+        <v>2526.038</v>
       </c>
       <c r="F92">
-        <v>2728.62</v>
+        <v>2758.938</v>
       </c>
       <c r="G92">
         <v>74.3</v>
@@ -8825,37 +8825,37 @@
         <v>309.1</v>
       </c>
       <c r="M92">
-        <v>547.9068960000001</v>
+        <v>553.9947504</v>
       </c>
       <c r="N92">
-        <v>-238.8068960000001</v>
+        <v>-244.8947504</v>
       </c>
       <c r="O92">
-        <v>-59.70172400000001</v>
+        <v>-61.22368760000001</v>
       </c>
       <c r="P92">
-        <v>-179.105172</v>
+        <v>-183.6710628</v>
       </c>
       <c r="Q92">
-        <v>-94.80517200000008</v>
+        <v>-99.37106280000006</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.048965489468623</v>
+        <v>1.160428321631804</v>
       </c>
       <c r="T92">
-        <v>8.59289862501241</v>
+        <v>9.547665138902678</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.141036735555159</v>
+        <v>0.1394868813182891</v>
       </c>
       <c r="W92">
-        <v>0.1724798235005241</v>
+        <v>0.1727910342312876</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.564146942220636</v>
+        <v>0.5579475252731565</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.261678390097334</v>
+        <v>0.263228390097334</v>
       </c>
       <c r="C93">
-        <v>-1102.291153932058</v>
+        <v>-1143.889362603555</v>
       </c>
       <c r="D93">
-        <v>1582.346846067942</v>
+        <v>1571.066637396446</v>
       </c>
       <c r="E93">
-        <v>2526.038</v>
+        <v>2556.356</v>
       </c>
       <c r="F93">
-        <v>2758.938</v>
+        <v>2789.256</v>
       </c>
       <c r="G93">
         <v>74.3</v>
@@ -8907,37 +8907,37 @@
         <v>309.1</v>
       </c>
       <c r="M93">
-        <v>553.9947504</v>
+        <v>560.0826048000001</v>
       </c>
       <c r="N93">
-        <v>-244.8947504</v>
+        <v>-250.9826048000001</v>
       </c>
       <c r="O93">
-        <v>-61.22368760000001</v>
+        <v>-62.74565120000003</v>
       </c>
       <c r="P93">
-        <v>-183.6710628</v>
+        <v>-188.2369536000001</v>
       </c>
       <c r="Q93">
-        <v>-99.37106280000006</v>
+        <v>-103.9369536000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.160428321631804</v>
+        <v>1.29975686183578</v>
       </c>
       <c r="T93">
-        <v>9.547665138902678</v>
+        <v>10.74112328126552</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1394868813182891</v>
+        <v>0.1379707195648294</v>
       </c>
       <c r="W93">
-        <v>0.1727910342312876</v>
+        <v>0.1730954795113823</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5579475252731565</v>
+        <v>0.5518828782593177</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.263228390097334</v>
+        <v>0.264778390097334</v>
       </c>
       <c r="C94">
-        <v>-1143.889362603555</v>
+        <v>-1185.327881330915</v>
       </c>
       <c r="D94">
-        <v>1571.066637396446</v>
+        <v>1559.946118669086</v>
       </c>
       <c r="E94">
-        <v>2556.356</v>
+        <v>2586.674</v>
       </c>
       <c r="F94">
-        <v>2789.256</v>
+        <v>2819.574000000001</v>
       </c>
       <c r="G94">
         <v>74.3</v>
@@ -8989,37 +8989,37 @@
         <v>309.1</v>
       </c>
       <c r="M94">
-        <v>560.0826048000001</v>
+        <v>566.1704592000001</v>
       </c>
       <c r="N94">
-        <v>-250.9826048000001</v>
+        <v>-257.0704592000001</v>
       </c>
       <c r="O94">
-        <v>-62.74565120000003</v>
+        <v>-64.26761480000002</v>
       </c>
       <c r="P94">
-        <v>-188.2369536000001</v>
+        <v>-192.8028444000001</v>
       </c>
       <c r="Q94">
-        <v>-103.9369536000001</v>
+        <v>-108.5028444000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.29975686183578</v>
+        <v>1.478893556383748</v>
       </c>
       <c r="T94">
-        <v>10.74112328126552</v>
+        <v>12.27556946430345</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1379707195648294</v>
+        <v>0.1364871634404764</v>
       </c>
       <c r="W94">
-        <v>0.1730954795113823</v>
+        <v>0.1733933775811523</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5518828782593177</v>
+        <v>0.5459486537619057</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.264778390097334</v>
+        <v>0.266328390097334</v>
       </c>
       <c r="C95">
-        <v>-1185.327881330915</v>
+        <v>-1226.61007729167</v>
       </c>
       <c r="D95">
-        <v>1559.946118669086</v>
+        <v>1548.981922708331</v>
       </c>
       <c r="E95">
-        <v>2586.674</v>
+        <v>2616.992</v>
       </c>
       <c r="F95">
-        <v>2819.574000000001</v>
+        <v>2849.892</v>
       </c>
       <c r="G95">
         <v>74.3</v>
@@ -9071,37 +9071,37 @@
         <v>309.1</v>
       </c>
       <c r="M95">
-        <v>566.1704592000001</v>
+        <v>572.2583136000001</v>
       </c>
       <c r="N95">
-        <v>-257.0704592000001</v>
+        <v>-263.1583136</v>
       </c>
       <c r="O95">
-        <v>-64.26761480000002</v>
+        <v>-65.78957840000001</v>
       </c>
       <c r="P95">
-        <v>-192.8028444000001</v>
+        <v>-197.3687352</v>
       </c>
       <c r="Q95">
-        <v>-108.5028444000001</v>
+        <v>-113.0687352000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.478893556383748</v>
+        <v>1.717742482447707</v>
       </c>
       <c r="T95">
-        <v>12.27556946430345</v>
+        <v>14.32149770835403</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1364871634404764</v>
+        <v>0.1350351723400458</v>
       </c>
       <c r="W95">
-        <v>0.1733933775811523</v>
+        <v>0.1736849373941188</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5459486537619057</v>
+        <v>0.5401406893601833</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.266328390097334</v>
+        <v>0.267878390097334</v>
       </c>
       <c r="C96">
-        <v>-1226.61007729167</v>
+        <v>-1267.739223658255</v>
       </c>
       <c r="D96">
-        <v>1548.981922708331</v>
+        <v>1538.170776341746</v>
       </c>
       <c r="E96">
-        <v>2616.992</v>
+        <v>2647.31</v>
       </c>
       <c r="F96">
-        <v>2849.892</v>
+        <v>2880.21</v>
       </c>
       <c r="G96">
         <v>74.3</v>
@@ -9153,37 +9153,37 @@
         <v>309.1</v>
       </c>
       <c r="M96">
-        <v>572.2583136000001</v>
+        <v>578.3461680000001</v>
       </c>
       <c r="N96">
-        <v>-263.1583136</v>
+        <v>-269.2461680000001</v>
       </c>
       <c r="O96">
-        <v>-65.78957840000001</v>
+        <v>-67.31154200000003</v>
       </c>
       <c r="P96">
-        <v>-197.3687352</v>
+        <v>-201.9346260000001</v>
       </c>
       <c r="Q96">
-        <v>-113.0687352000001</v>
+        <v>-117.6346260000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.717742482447707</v>
+        <v>2.052130978937249</v>
       </c>
       <c r="T96">
-        <v>14.32149770835403</v>
+        <v>17.18579725002484</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1350351723400458</v>
+        <v>0.1336137494733085</v>
       </c>
       <c r="W96">
-        <v>0.1736849373941188</v>
+        <v>0.1739703591057597</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5401406893601833</v>
+        <v>0.534454997893234</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.267878390097334</v>
+        <v>0.269428390097334</v>
       </c>
       <c r="C97">
-        <v>-1267.739223658255</v>
+        <v>-1308.71850285582</v>
       </c>
       <c r="D97">
-        <v>1538.170776341746</v>
+        <v>1527.50949714418</v>
       </c>
       <c r="E97">
-        <v>2647.31</v>
+        <v>2677.628</v>
       </c>
       <c r="F97">
-        <v>2880.21</v>
+        <v>2910.528</v>
       </c>
       <c r="G97">
         <v>74.3</v>
@@ -9235,37 +9235,37 @@
         <v>309.1</v>
       </c>
       <c r="M97">
-        <v>578.3461680000001</v>
+        <v>584.4340224000001</v>
       </c>
       <c r="N97">
-        <v>-269.2461680000001</v>
+        <v>-275.3340224000001</v>
       </c>
       <c r="O97">
-        <v>-67.31154200000003</v>
+        <v>-68.83350560000002</v>
       </c>
       <c r="P97">
-        <v>-201.9346260000001</v>
+        <v>-206.5005168000001</v>
       </c>
       <c r="Q97">
-        <v>-117.6346260000001</v>
+        <v>-122.2005168000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.052130978937249</v>
+        <v>2.553713723671562</v>
       </c>
       <c r="T97">
-        <v>17.18579725002484</v>
+        <v>21.48224656253106</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1336137494733085</v>
+        <v>0.1322219395829616</v>
       </c>
       <c r="W97">
-        <v>0.1739703591057597</v>
+        <v>0.1742498345317413</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.534454997893234</v>
+        <v>0.5288877583318461</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2694283900973339</v>
+        <v>0.270978390097334</v>
       </c>
       <c r="C98">
-        <v>-1308.71850285582</v>
+        <v>-1349.551009685494</v>
       </c>
       <c r="D98">
-        <v>1527.509497144181</v>
+        <v>1516.994990314506</v>
       </c>
       <c r="E98">
-        <v>2677.628</v>
+        <v>2707.946</v>
       </c>
       <c r="F98">
-        <v>2910.528</v>
+        <v>2940.846</v>
       </c>
       <c r="G98">
         <v>74.3</v>
@@ -9317,37 +9317,37 @@
         <v>309.1</v>
       </c>
       <c r="M98">
-        <v>584.4340224000001</v>
+        <v>590.5218768</v>
       </c>
       <c r="N98">
-        <v>-275.3340224000001</v>
+        <v>-281.4218767999999</v>
       </c>
       <c r="O98">
-        <v>-68.83350560000002</v>
+        <v>-70.35546919999999</v>
       </c>
       <c r="P98">
-        <v>-206.5005168000001</v>
+        <v>-211.0664076</v>
       </c>
       <c r="Q98">
-        <v>-122.2005168000001</v>
+        <v>-126.7664076</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.553713723671555</v>
+        <v>3.389684964895407</v>
       </c>
       <c r="T98">
-        <v>21.482246562531</v>
+        <v>28.64299541670801</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1322219395829616</v>
+        <v>0.1308588268037558</v>
       </c>
       <c r="W98">
-        <v>0.1742498345317413</v>
+        <v>0.1745235475778058</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5288877583318461</v>
+        <v>0.5234353072150231</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.270978390097334</v>
+        <v>0.272528390097334</v>
       </c>
       <c r="C99">
-        <v>-1349.551009685494</v>
+        <v>-1390.239754319539</v>
       </c>
       <c r="D99">
-        <v>1516.994990314506</v>
+        <v>1506.624245680462</v>
       </c>
       <c r="E99">
-        <v>2707.946</v>
+        <v>2738.264</v>
       </c>
       <c r="F99">
-        <v>2940.846</v>
+        <v>2971.164</v>
       </c>
       <c r="G99">
         <v>74.3</v>
@@ -9399,37 +9399,37 @@
         <v>309.1</v>
       </c>
       <c r="M99">
-        <v>590.5218768</v>
+        <v>596.6097312000001</v>
       </c>
       <c r="N99">
-        <v>-281.4218767999999</v>
+        <v>-287.5097312</v>
       </c>
       <c r="O99">
-        <v>-70.35546919999999</v>
+        <v>-71.87743280000001</v>
       </c>
       <c r="P99">
-        <v>-211.0664076</v>
+        <v>-215.6322984</v>
       </c>
       <c r="Q99">
-        <v>-126.7664076</v>
+        <v>-131.3322984000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.389684964895407</v>
+        <v>5.061627447343111</v>
       </c>
       <c r="T99">
-        <v>28.64299541670801</v>
+        <v>42.96449312506201</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1308588268037558</v>
+        <v>0.129523532652697</v>
       </c>
       <c r="W99">
-        <v>0.1745235475778058</v>
+        <v>0.1747916746433384</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5234353072150231</v>
+        <v>0.5180941306107881</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.272528390097334</v>
+        <v>0.274078390097334</v>
       </c>
       <c r="C100">
-        <v>-1390.239754319539</v>
+        <v>-1430.787665174478</v>
       </c>
       <c r="D100">
-        <v>1506.624245680462</v>
+        <v>1496.394334825522</v>
       </c>
       <c r="E100">
-        <v>2738.264</v>
+        <v>2768.582</v>
       </c>
       <c r="F100">
-        <v>2971.164</v>
+        <v>3001.482</v>
       </c>
       <c r="G100">
         <v>74.3</v>
@@ -9481,37 +9481,37 @@
         <v>309.1</v>
       </c>
       <c r="M100">
-        <v>596.6097312000001</v>
+        <v>602.6975856</v>
       </c>
       <c r="N100">
-        <v>-287.5097312</v>
+        <v>-293.5975856</v>
       </c>
       <c r="O100">
-        <v>-71.87743280000001</v>
+        <v>-73.3993964</v>
       </c>
       <c r="P100">
-        <v>-215.6322984</v>
+        <v>-220.1981892</v>
       </c>
       <c r="Q100">
-        <v>-131.3322984000001</v>
+        <v>-135.8981892</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.061627447343111</v>
+        <v>10.07745489468622</v>
       </c>
       <c r="T100">
-        <v>42.96449312506201</v>
+        <v>85.92898625012401</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.129523532652697</v>
+        <v>0.1282152141410536</v>
       </c>
       <c r="W100">
-        <v>0.1747916746433384</v>
+        <v>0.1750543850004764</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5180941306107881</v>
+        <v>0.5128608565642145</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.274078390097334</v>
-      </c>
-      <c r="C101">
-        <v>-1430.787665174478</v>
-      </c>
-      <c r="D101">
-        <v>1496.394334825522</v>
-      </c>
-      <c r="E101">
-        <v>2768.582</v>
-      </c>
-      <c r="F101">
-        <v>3001.482</v>
-      </c>
-      <c r="G101">
-        <v>74.3</v>
-      </c>
-      <c r="H101">
-        <v>2798.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>393.4</v>
-      </c>
-      <c r="K101">
-        <v>84.29999999999995</v>
-      </c>
-      <c r="L101">
-        <v>309.1</v>
-      </c>
-      <c r="M101">
-        <v>602.6975856</v>
-      </c>
-      <c r="N101">
-        <v>-293.5975856</v>
-      </c>
-      <c r="O101">
-        <v>-73.3993964</v>
-      </c>
-      <c r="P101">
-        <v>-220.1981892</v>
-      </c>
-      <c r="Q101">
-        <v>-135.8981892</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.07745489468622</v>
-      </c>
-      <c r="T101">
-        <v>85.92898625012401</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1282152141410536</v>
-      </c>
-      <c r="W101">
-        <v>0.1750543850004764</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5128608565642145</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
